--- a/rapporten/dagrapport.xlsx
+++ b/rapporten/dagrapport.xlsx
@@ -485,7 +485,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="10100"/>
-          <min val="9500"/>
+          <min val="9750"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -518,7 +518,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="100"/>
+        <majorUnit val="50"/>
       </valAx>
     </plotArea>
     <legend>
@@ -883,7 +883,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="135"/>
-          <min val="115"/>
+          <min val="110"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5649,7 +5649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C35"/>
+  <dimension ref="B1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9639.620000000001</v>
+        <v>9803.040000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-360.38</v>
+        <v>-196.96</v>
       </c>
     </row>
     <row r="7">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.0360379999999999</v>
+        <v>-0.01969599999999994</v>
       </c>
     </row>
     <row r="8">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>-346</v>
+        <v>-182.5799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>-0.01892322732749618</v>
+        <v>-0.01465507763084839</v>
       </c>
     </row>
     <row r="11">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10029.19</v>
+        <v>10024.69</v>
       </c>
     </row>
     <row r="15">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>29.19</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="16">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.002919000000000116</v>
+        <v>0.002469000000000054</v>
       </c>
     </row>
     <row r="17">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>14.77000000000044</v>
+        <v>10.27000000000044</v>
       </c>
     </row>
     <row r="18">
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.01720147235573777</v>
+        <v>0.004654736380648616</v>
       </c>
     </row>
     <row r="20">
@@ -5879,7 +5879,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="38.8" customHeight="1">
+    <row r="28" ht="21.4" customHeight="1">
       <c r="B28" s="13" t="inlineStr">
         <is>
           <t>•</t>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 52% in een stijgende trend).</t>
+          <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
@@ -5899,43 +5899,55 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
+          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38.8" customHeight="1">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
           <t>3 van de 5 sterkste staan al ver boven hun gemiddelde (SHELL.AS, WKL.AS, XOM): de trend is sterk, maar instappen op zo'n moment kost vaker een terugval.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="21.4" customHeight="1">
-      <c r="B30" s="13" t="inlineStr">
+    <row r="31" ht="21.4" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="12" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Vandaag gekocht en verkocht</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="21.4" customHeight="1">
-      <c r="B33" s="13" t="inlineStr">
+    <row r="34" ht="21.4" customHeight="1">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>Niets gekocht of verkocht.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Meer weten? Zie de tabbladen hieronder: Grafieken, Analyse, Verlies en risico, Kansen, Klaar voor echt geld.</t>
         </is>
@@ -5980,7 +5992,7 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-normaal.</t>
+          <t>Investeerder: status OK, 52 van 52 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6004,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6016,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-normaal.</t>
+          <t>Trend-agent: status OK, 50 van 50 koersen opgehaald, marktregime stijgend-laag.</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6028,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6715,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -6729,7 +6741,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC2" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -6779,49 +6791,49 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>63551.8711</v>
+        <v>63910.1758</v>
       </c>
       <c r="AW2" t="n">
-        <v>64381.0781</v>
+        <v>64433.6797</v>
       </c>
       <c r="AX2" t="n">
-        <v>63251.1133</v>
+        <v>63185.4727</v>
       </c>
       <c r="AY2" t="n">
-        <v>63402.4336</v>
+        <v>63551.875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>63337.5587</v>
+        <v>63322.8705</v>
       </c>
       <c r="BA2" t="n">
-        <v>69743.889</v>
+        <v>69872.4305</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="BD2" t="n">
+        <v>1871.2637</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1895.7494</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1852.8403</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1881.3735</v>
       </c>
-      <c r="BE2" t="n">
-        <v>1921.7754</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1873.3473</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1878.135</v>
-      </c>
       <c r="BH2" t="n">
-        <v>1812.4882</v>
+        <v>1808.2342</v>
       </c>
       <c r="BI2" t="n">
-        <v>2033.9537</v>
+        <v>2039.3067</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -6978,7 +6990,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -7004,7 +7016,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC3" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -7054,49 +7066,49 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>63404.4258</v>
+        <v>63551.8711</v>
       </c>
       <c r="AW3" t="n">
-        <v>63926.332</v>
+        <v>64381.0781</v>
       </c>
       <c r="AX3" t="n">
-        <v>62799.2891</v>
+        <v>63251.1133</v>
       </c>
       <c r="AY3" t="n">
-        <v>63402.1719</v>
+        <v>63402.4336</v>
       </c>
       <c r="AZ3" t="n">
-        <v>63385.6995</v>
+        <v>63337.5587</v>
       </c>
       <c r="BA3" t="n">
-        <v>69628.03879999999</v>
+        <v>69743.889</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1878.1885</v>
+        <v>1881.3735</v>
       </c>
       <c r="BE3" t="n">
-        <v>1898.2252</v>
+        <v>1921.7754</v>
       </c>
       <c r="BF3" t="n">
-        <v>1861.9204</v>
+        <v>1873.3473</v>
       </c>
       <c r="BG3" t="n">
-        <v>1883.9913</v>
+        <v>1878.135</v>
       </c>
       <c r="BH3" t="n">
-        <v>1817.7695</v>
+        <v>1812.4882</v>
       </c>
       <c r="BI3" t="n">
-        <v>2029.2941</v>
+        <v>2033.9537</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
@@ -7259,7 +7271,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -7285,7 +7297,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC4" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -7335,49 +7347,49 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>63402.0898</v>
+        <v>63404.4258</v>
       </c>
       <c r="AW4" t="n">
-        <v>63551.5625</v>
+        <v>63926.332</v>
       </c>
       <c r="AX4" t="n">
-        <v>62487.6992</v>
+        <v>62799.2891</v>
       </c>
       <c r="AY4" t="n">
-        <v>62975.5938</v>
+        <v>63402.1719</v>
       </c>
       <c r="AZ4" t="n">
-        <v>63450.7779</v>
+        <v>63385.6995</v>
       </c>
       <c r="BA4" t="n">
-        <v>69501.5811</v>
+        <v>69628.03879999999</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1884.017</v>
+        <v>1878.1885</v>
       </c>
       <c r="BE4" t="n">
-        <v>1889.2706</v>
+        <v>1898.2252</v>
       </c>
       <c r="BF4" t="n">
-        <v>1862.5646</v>
+        <v>1861.9204</v>
       </c>
       <c r="BG4" t="n">
-        <v>1880.65</v>
+        <v>1883.9913</v>
       </c>
       <c r="BH4" t="n">
-        <v>1824.0862</v>
+        <v>1817.7695</v>
       </c>
       <c r="BI4" t="n">
-        <v>2024.0651</v>
+        <v>2029.2941</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -7477,13 +7489,13 @@
         </is>
       </c>
       <c r="KO4" t="n">
-        <v>9639.620000000001</v>
+        <v>9803.040000000001</v>
       </c>
       <c r="KP4" t="n">
-        <v>10029.19</v>
+        <v>10024.69</v>
       </c>
       <c r="KQ4" t="n">
-        <v>9828.58</v>
+        <v>9949.379999999999</v>
       </c>
       <c r="KR4" t="n">
         <v>10000</v>
@@ -7540,7 +7552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -7566,7 +7578,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC5" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -7616,49 +7628,49 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>15 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>62974.3359</v>
+        <v>63402.0898</v>
       </c>
       <c r="AW5" t="n">
-        <v>63119.1328</v>
+        <v>63551.5625</v>
       </c>
       <c r="AX5" t="n">
-        <v>62850.9609</v>
+        <v>62487.6992</v>
       </c>
       <c r="AY5" t="n">
-        <v>63024.3203</v>
+        <v>62975.5938</v>
       </c>
       <c r="AZ5" t="n">
-        <v>63510.9357</v>
+        <v>63450.7779</v>
       </c>
       <c r="BA5" t="n">
-        <v>69371.18979999999</v>
+        <v>69501.5811</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>15 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1880.613</v>
+        <v>1884.017</v>
       </c>
       <c r="BE5" t="n">
-        <v>1884.718</v>
+        <v>1889.2706</v>
       </c>
       <c r="BF5" t="n">
-        <v>1874.328</v>
+        <v>1862.5646</v>
       </c>
       <c r="BG5" t="n">
-        <v>1880.9083</v>
+        <v>1880.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>1830.1721</v>
+        <v>1824.0862</v>
       </c>
       <c r="BI5" t="n">
-        <v>2018.3586</v>
+        <v>2024.0651</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -7724,7 +7736,7 @@
         <v>865.3239</v>
       </c>
       <c r="CF5" t="n">
-        <v>937.4059</v>
+        <v>937.4059999999999</v>
       </c>
       <c r="CG5" t="n">
         <v>486.3243</v>
@@ -7810,7 +7822,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -7839,7 +7851,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC6" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -7889,49 +7901,49 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>16 aug</t>
+          <t>15 aug</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>63023.4219</v>
+        <v>62974.3359</v>
       </c>
       <c r="AW6" t="n">
-        <v>63310.7773</v>
+        <v>63119.1328</v>
       </c>
       <c r="AX6" t="n">
-        <v>62648.5742</v>
+        <v>62850.9609</v>
       </c>
       <c r="AY6" t="n">
-        <v>62818.6523</v>
+        <v>63024.3203</v>
       </c>
       <c r="AZ6" t="n">
-        <v>63568.5068</v>
+        <v>63510.9357</v>
       </c>
       <c r="BA6" t="n">
-        <v>69239.3602</v>
+        <v>69371.18979999999</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>16 aug</t>
+          <t>15 aug</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1880.8916</v>
+        <v>1880.613</v>
       </c>
       <c r="BE6" t="n">
-        <v>1889.6053</v>
+        <v>1884.718</v>
       </c>
       <c r="BF6" t="n">
-        <v>1867.8917</v>
+        <v>1874.328</v>
       </c>
       <c r="BG6" t="n">
-        <v>1873.943</v>
+        <v>1880.9083</v>
       </c>
       <c r="BH6" t="n">
-        <v>1836.2191</v>
+        <v>1830.1721</v>
       </c>
       <c r="BI6" t="n">
-        <v>2012.6952</v>
+        <v>2018.3586</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -8083,7 +8095,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -8112,7 +8124,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC7" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -8162,49 +8174,49 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>16 aug</t>
         </is>
       </c>
       <c r="AV7" t="n">
-        <v>62819.3789</v>
+        <v>63023.4219</v>
       </c>
       <c r="AW7" t="n">
-        <v>64547.8477</v>
+        <v>63310.7773</v>
       </c>
       <c r="AX7" t="n">
-        <v>62687.1016</v>
+        <v>62648.5742</v>
       </c>
       <c r="AY7" t="n">
-        <v>64506.2539</v>
+        <v>62818.6523</v>
       </c>
       <c r="AZ7" t="n">
-        <v>63667.9851</v>
+        <v>63568.5068</v>
       </c>
       <c r="BA7" t="n">
-        <v>69139.0836</v>
+        <v>69239.3602</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>16 aug</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1873.97</v>
+        <v>1880.8916</v>
       </c>
       <c r="BE7" t="n">
-        <v>1916.6569</v>
+        <v>1889.6053</v>
       </c>
       <c r="BF7" t="n">
-        <v>1870.7479</v>
+        <v>1867.8917</v>
       </c>
       <c r="BG7" t="n">
-        <v>1912.2021</v>
+        <v>1873.943</v>
       </c>
       <c r="BH7" t="n">
-        <v>1843.056</v>
+        <v>1836.2191</v>
       </c>
       <c r="BI7" t="n">
-        <v>2008.1651</v>
+        <v>2012.6952</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -8270,7 +8282,7 @@
         <v>959.329</v>
       </c>
       <c r="CF7" t="n">
-        <v>948.1457</v>
+        <v>948.1458</v>
       </c>
       <c r="CG7" t="n">
         <v>494.148</v>
@@ -8356,7 +8368,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -8385,7 +8397,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC8" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -8435,49 +8447,49 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>64506.5234</v>
+        <v>62819.3789</v>
       </c>
       <c r="AW8" t="n">
-        <v>64987.7109</v>
+        <v>64547.8477</v>
       </c>
       <c r="AX8" t="n">
-        <v>63980.3242</v>
+        <v>62687.1016</v>
       </c>
       <c r="AY8" t="n">
-        <v>64680.7109</v>
+        <v>64506.2539</v>
       </c>
       <c r="AZ8" t="n">
-        <v>63758.8317</v>
+        <v>63667.9851</v>
       </c>
       <c r="BA8" t="n">
-        <v>69041.8438</v>
+        <v>69139.0836</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1912.2086</v>
+        <v>1873.97</v>
       </c>
       <c r="BE8" t="n">
-        <v>1920.5233</v>
+        <v>1916.6569</v>
       </c>
       <c r="BF8" t="n">
-        <v>1884.4778</v>
+        <v>1870.7479</v>
       </c>
       <c r="BG8" t="n">
-        <v>1916.4596</v>
+        <v>1912.2021</v>
       </c>
       <c r="BH8" t="n">
-        <v>1849.181</v>
+        <v>1843.056</v>
       </c>
       <c r="BI8" t="n">
-        <v>2004.2355</v>
+        <v>2008.1651</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -8629,7 +8641,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -8658,7 +8670,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC9" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -8708,49 +8720,49 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>64680.0469</v>
+        <v>64506.5234</v>
       </c>
       <c r="AW9" t="n">
-        <v>69996.9531</v>
+        <v>64987.7109</v>
       </c>
       <c r="AX9" t="n">
-        <v>64111.0703</v>
+        <v>63980.3242</v>
       </c>
       <c r="AY9" t="n">
-        <v>69266.1875</v>
+        <v>64680.7109</v>
       </c>
       <c r="AZ9" t="n">
-        <v>63972.9783</v>
+        <v>63758.8317</v>
       </c>
       <c r="BA9" t="n">
-        <v>68995.0692</v>
+        <v>69041.8438</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1916.4268</v>
+        <v>1912.2086</v>
       </c>
       <c r="BE9" t="n">
-        <v>2327.7012</v>
+        <v>1920.5233</v>
       </c>
       <c r="BF9" t="n">
-        <v>1905.0824</v>
+        <v>1884.4778</v>
       </c>
       <c r="BG9" t="n">
-        <v>2251.458</v>
+        <v>1916.4596</v>
       </c>
       <c r="BH9" t="n">
-        <v>1862.8185</v>
+        <v>1849.181</v>
       </c>
       <c r="BI9" t="n">
-        <v>2003.2673</v>
+        <v>2004.2355</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -8816,7 +8828,7 @@
         <v>920.8051</v>
       </c>
       <c r="CF9" t="n">
-        <v>955.1344</v>
+        <v>955.1345</v>
       </c>
       <c r="CG9" t="n">
         <v>501.8105</v>
@@ -8902,7 +8914,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -8931,7 +8943,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC10" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -8981,49 +8993,49 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="AV10" t="n">
-        <v>69268.25</v>
+        <v>64680.0469</v>
       </c>
       <c r="AW10" t="n">
-        <v>73369.80469999999</v>
+        <v>69996.9531</v>
       </c>
       <c r="AX10" t="n">
-        <v>68867.5312</v>
+        <v>64111.0703</v>
       </c>
       <c r="AY10" t="n">
-        <v>73032.75780000001</v>
+        <v>69266.1875</v>
       </c>
       <c r="AZ10" t="n">
-        <v>64233.5583</v>
+        <v>63972.9783</v>
       </c>
       <c r="BA10" t="n">
-        <v>68975.36079999999</v>
+        <v>68995.0692</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2251.4441</v>
+        <v>1916.4268</v>
       </c>
       <c r="BE10" t="n">
-        <v>2357.2283</v>
+        <v>2327.7012</v>
       </c>
       <c r="BF10" t="n">
-        <v>2222.5747</v>
+        <v>1905.0824</v>
       </c>
       <c r="BG10" t="n">
-        <v>2326.3848</v>
+        <v>2251.458</v>
       </c>
       <c r="BH10" t="n">
-        <v>1877.167</v>
+        <v>1862.8185</v>
       </c>
       <c r="BI10" t="n">
-        <v>2003.5594</v>
+        <v>2003.2673</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -9175,7 +9187,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -9204,7 +9216,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC11" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -9254,49 +9266,49 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="AV11" t="n">
-        <v>73031.08590000001</v>
+        <v>69268.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>79463.71090000001</v>
+        <v>73369.80469999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>73011.41409999999</v>
+        <v>68867.5312</v>
       </c>
       <c r="AY11" t="n">
-        <v>78335.1875</v>
+        <v>73032.75780000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>64570.556</v>
+        <v>64233.5583</v>
       </c>
       <c r="BA11" t="n">
-        <v>68973.5929</v>
+        <v>68975.36079999999</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2326.3823</v>
+        <v>2251.4441</v>
       </c>
       <c r="BE11" t="n">
-        <v>2545.8811</v>
+        <v>2357.2283</v>
       </c>
       <c r="BF11" t="n">
-        <v>2324.7095</v>
+        <v>2222.5747</v>
       </c>
       <c r="BG11" t="n">
-        <v>2515.2817</v>
+        <v>2326.3848</v>
       </c>
       <c r="BH11" t="n">
-        <v>1893.5093</v>
+        <v>1877.167</v>
       </c>
       <c r="BI11" t="n">
-        <v>2004.4141</v>
+        <v>2003.5594</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -9448,7 +9460,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -9477,7 +9489,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC12" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9523,53 +9535,53 @@
         <v>1535.0628</v>
       </c>
       <c r="AS12" t="n">
-        <v>1201.4255</v>
+        <v>1201.4256</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>22 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="AV12" t="n">
-        <v>78332.55469999999</v>
+        <v>73031.08590000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>78801.14840000001</v>
+        <v>79463.71090000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>76526.71090000001</v>
+        <v>73011.41409999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>77083.41409999999</v>
+        <v>78335.1875</v>
       </c>
       <c r="AZ12" t="n">
-        <v>64861.3403</v>
+        <v>64570.556</v>
       </c>
       <c r="BA12" t="n">
-        <v>68980.8422</v>
+        <v>68973.5929</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>22 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2515.3923</v>
+        <v>2326.3823</v>
       </c>
       <c r="BE12" t="n">
-        <v>2528.8967</v>
+        <v>2545.8811</v>
       </c>
       <c r="BF12" t="n">
-        <v>2389.9021</v>
+        <v>2324.7095</v>
       </c>
       <c r="BG12" t="n">
-        <v>2424.2512</v>
+        <v>2515.2817</v>
       </c>
       <c r="BH12" t="n">
-        <v>1906.8639</v>
+        <v>1893.5093</v>
       </c>
       <c r="BI12" t="n">
-        <v>2005.3975</v>
+        <v>2004.4141</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -9635,7 +9647,7 @@
         <v>738.8837</v>
       </c>
       <c r="CF12" t="n">
-        <v>958.2496</v>
+        <v>958.2497</v>
       </c>
       <c r="CG12" t="n">
         <v>511.2377</v>
@@ -9721,7 +9733,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -9750,7 +9762,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC13" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -9796,53 +9808,53 @@
         <v>1535.6006</v>
       </c>
       <c r="AS13" t="n">
-        <v>1204.238</v>
+        <v>1204.2381</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>23 aug</t>
+          <t>22 aug</t>
         </is>
       </c>
       <c r="AV13" t="n">
-        <v>77082.8438</v>
+        <v>78332.55469999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>78036.86719999999</v>
+        <v>78801.14840000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>75624.94530000001</v>
+        <v>76526.71090000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>77755.2656</v>
+        <v>77083.41409999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>65154.6795</v>
+        <v>64861.3403</v>
       </c>
       <c r="BA13" t="n">
-        <v>69004.52</v>
+        <v>68980.8422</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>23 aug</t>
+          <t>22 aug</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>2424.217</v>
+        <v>2515.3923</v>
       </c>
       <c r="BE13" t="n">
-        <v>2483.9304</v>
+        <v>2528.8967</v>
       </c>
       <c r="BF13" t="n">
-        <v>2357.1399</v>
+        <v>2389.9021</v>
       </c>
       <c r="BG13" t="n">
-        <v>2463.8159</v>
+        <v>2424.2512</v>
       </c>
       <c r="BH13" t="n">
-        <v>1920.5596</v>
+        <v>1906.8639</v>
       </c>
       <c r="BI13" t="n">
-        <v>2006.9991</v>
+        <v>2005.3975</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -9994,7 +10006,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -10023,7 +10035,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC14" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -10073,49 +10085,49 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>23 aug</t>
         </is>
       </c>
       <c r="AV14" t="n">
-        <v>77748.875</v>
+        <v>77082.8438</v>
       </c>
       <c r="AW14" t="n">
-        <v>79970.1094</v>
+        <v>78036.86719999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>76688.8281</v>
+        <v>75624.94530000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>78964.4844</v>
+        <v>77755.2656</v>
       </c>
       <c r="AZ14" t="n">
-        <v>65463.0116</v>
+        <v>65154.6795</v>
       </c>
       <c r="BA14" t="n">
-        <v>69085.83199999999</v>
+        <v>69004.52</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>23 aug</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>2463.6406</v>
+        <v>2424.217</v>
       </c>
       <c r="BE14" t="n">
-        <v>2531.7449</v>
+        <v>2483.9304</v>
       </c>
       <c r="BF14" t="n">
-        <v>2425.3879</v>
+        <v>2357.1399</v>
       </c>
       <c r="BG14" t="n">
-        <v>2481.8313</v>
+        <v>2463.8159</v>
       </c>
       <c r="BH14" t="n">
-        <v>1934.5361</v>
+        <v>1920.5596</v>
       </c>
       <c r="BI14" t="n">
-        <v>2010.2998</v>
+        <v>2006.9991</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -10267,7 +10279,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -10296,7 +10308,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC15" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -10346,49 +10358,49 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="AV15" t="n">
-        <v>78960.0938</v>
+        <v>77748.875</v>
       </c>
       <c r="AW15" t="n">
-        <v>81235.0312</v>
+        <v>79970.1094</v>
       </c>
       <c r="AX15" t="n">
-        <v>77870.625</v>
+        <v>76688.8281</v>
       </c>
       <c r="AY15" t="n">
-        <v>78564.97659999999</v>
+        <v>78964.4844</v>
       </c>
       <c r="AZ15" t="n">
-        <v>65754.4108</v>
+        <v>65463.0116</v>
       </c>
       <c r="BA15" t="n">
-        <v>69125.8799</v>
+        <v>69085.83199999999</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2481.7778</v>
+        <v>2463.6406</v>
       </c>
       <c r="BE15" t="n">
-        <v>2531.0845</v>
+        <v>2531.7449</v>
       </c>
       <c r="BF15" t="n">
-        <v>2416.6028</v>
+        <v>2425.3879</v>
       </c>
       <c r="BG15" t="n">
-        <v>2443.1594</v>
+        <v>2481.8313</v>
       </c>
       <c r="BH15" t="n">
-        <v>1947.4478</v>
+        <v>1934.5361</v>
       </c>
       <c r="BI15" t="n">
-        <v>2012.1987</v>
+        <v>2010.2998</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -10540,7 +10552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -10569,7 +10581,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC16" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -10619,49 +10631,49 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="AV16" t="n">
-        <v>78538.58590000001</v>
+        <v>78960.0938</v>
       </c>
       <c r="AW16" t="n">
-        <v>79240.5</v>
+        <v>81235.0312</v>
       </c>
       <c r="AX16" t="n">
-        <v>77639.83590000001</v>
+        <v>77870.625</v>
       </c>
       <c r="AY16" t="n">
-        <v>79027.4219</v>
+        <v>78564.97659999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>66069.0113</v>
+        <v>65754.4108</v>
       </c>
       <c r="BA16" t="n">
-        <v>69174.60709999999</v>
+        <v>69125.8799</v>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2442.4893</v>
+        <v>2481.7778</v>
       </c>
       <c r="BE16" t="n">
-        <v>2514.6663</v>
+        <v>2531.0845</v>
       </c>
       <c r="BF16" t="n">
-        <v>2432.5122</v>
+        <v>2416.6028</v>
       </c>
       <c r="BG16" t="n">
-        <v>2506.261</v>
+        <v>2443.1594</v>
       </c>
       <c r="BH16" t="n">
-        <v>1962.2028</v>
+        <v>1947.4478</v>
       </c>
       <c r="BI16" t="n">
-        <v>2014.2773</v>
+        <v>2012.1987</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -10813,7 +10825,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -10842,7 +10854,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC17" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -10888,53 +10900,53 @@
         <v>1541.0191</v>
       </c>
       <c r="AS17" t="n">
-        <v>1215.9398</v>
+        <v>1215.9399</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="AV17" t="n">
-        <v>79037.9219</v>
+        <v>78538.58590000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>80806.5625</v>
+        <v>79240.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>78591.10159999999</v>
+        <v>77639.83590000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>80257.53909999999</v>
+        <v>79027.4219</v>
       </c>
       <c r="AZ17" t="n">
-        <v>66429.01059999999</v>
+        <v>66069.0113</v>
       </c>
       <c r="BA17" t="n">
-        <v>69224.57120000001</v>
+        <v>69174.60709999999</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>2506.2395</v>
+        <v>2442.4893</v>
       </c>
       <c r="BE17" t="n">
-        <v>2564.2744</v>
+        <v>2514.6663</v>
       </c>
       <c r="BF17" t="n">
-        <v>2481.9448</v>
+        <v>2432.5122</v>
       </c>
       <c r="BG17" t="n">
-        <v>2510.4102</v>
+        <v>2506.261</v>
       </c>
       <c r="BH17" t="n">
-        <v>1977.5574</v>
+        <v>1962.2028</v>
       </c>
       <c r="BI17" t="n">
-        <v>2016.3855</v>
+        <v>2014.2773</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -11086,7 +11098,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -11115,7 +11127,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC18" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -11165,49 +11177,49 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="AV18" t="n">
-        <v>80264.64840000001</v>
+        <v>79037.9219</v>
       </c>
       <c r="AW18" t="n">
-        <v>81346.9531</v>
+        <v>80806.5625</v>
       </c>
       <c r="AX18" t="n">
-        <v>76909.35159999999</v>
+        <v>78591.10159999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>77830.28909999999</v>
+        <v>80257.53909999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>66721.7534</v>
+        <v>66429.01059999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>69263.11870000001</v>
+        <v>69224.57120000001</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>2510.6726</v>
+        <v>2506.2395</v>
       </c>
       <c r="BE18" t="n">
-        <v>2534.0122</v>
+        <v>2564.2744</v>
       </c>
       <c r="BF18" t="n">
-        <v>2408.7234</v>
+        <v>2481.9448</v>
       </c>
       <c r="BG18" t="n">
-        <v>2442.5359</v>
+        <v>2510.4102</v>
       </c>
       <c r="BH18" t="n">
-        <v>1991.5184</v>
+        <v>1977.5574</v>
       </c>
       <c r="BI18" t="n">
-        <v>2018.0803</v>
+        <v>2016.3855</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -11359,7 +11371,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -11388,7 +11400,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC19" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -11438,49 +11450,49 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>29 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="AV19" t="n">
-        <v>77830.8906</v>
+        <v>80264.64840000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>78327.94530000001</v>
+        <v>81346.9531</v>
       </c>
       <c r="AX19" t="n">
-        <v>77381.89840000001</v>
+        <v>76909.35159999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>78245.8125</v>
+        <v>77830.28909999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>67004.1269</v>
+        <v>66721.7534</v>
       </c>
       <c r="BA19" t="n">
-        <v>69310.378</v>
+        <v>69263.11870000001</v>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>29 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>2442.5647</v>
+        <v>2510.6726</v>
       </c>
       <c r="BE19" t="n">
-        <v>2459.6292</v>
+        <v>2534.0122</v>
       </c>
       <c r="BF19" t="n">
-        <v>2430.811</v>
+        <v>2408.7234</v>
       </c>
       <c r="BG19" t="n">
-        <v>2457.6863</v>
+        <v>2442.5359</v>
       </c>
       <c r="BH19" t="n">
-        <v>2004.7583</v>
+        <v>1991.5184</v>
       </c>
       <c r="BI19" t="n">
-        <v>2020.2713</v>
+        <v>2018.0803</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -11546,7 +11558,7 @@
         <v>877.4319</v>
       </c>
       <c r="CF19" t="n">
-        <v>970.713</v>
+        <v>970.7131000000001</v>
       </c>
       <c r="CG19" t="n">
         <v>534.7758</v>
@@ -11632,7 +11644,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -11661,7 +11673,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC20" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -11711,49 +11723,49 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>30 aug</t>
+          <t>29 aug</t>
         </is>
       </c>
       <c r="AV20" t="n">
-        <v>78246.1719</v>
+        <v>77830.8906</v>
       </c>
       <c r="AW20" t="n">
-        <v>79373.17969999999</v>
+        <v>78327.94530000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>77056.14840000001</v>
+        <v>77381.89840000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>77667.57030000001</v>
+        <v>78245.8125</v>
       </c>
       <c r="AZ20" t="n">
-        <v>67281.43769999999</v>
+        <v>67004.1269</v>
       </c>
       <c r="BA20" t="n">
-        <v>69363.75599999999</v>
+        <v>69310.378</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>30 aug</t>
+          <t>29 aug</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>2457.6919</v>
+        <v>2442.5647</v>
       </c>
       <c r="BE20" t="n">
-        <v>2532.959</v>
+        <v>2459.6292</v>
       </c>
       <c r="BF20" t="n">
-        <v>2389.4692</v>
+        <v>2430.811</v>
       </c>
       <c r="BG20" t="n">
-        <v>2417.9387</v>
+        <v>2457.6863</v>
       </c>
       <c r="BH20" t="n">
-        <v>2017.3551</v>
+        <v>2004.7583</v>
       </c>
       <c r="BI20" t="n">
-        <v>2022.6579</v>
+        <v>2020.2713</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -11905,7 +11917,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -11934,7 +11946,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC21" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -11984,49 +11996,49 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>30 aug</t>
         </is>
       </c>
       <c r="AV21" t="n">
-        <v>77673.7031</v>
+        <v>78246.1719</v>
       </c>
       <c r="AW21" t="n">
-        <v>79247.3438</v>
+        <v>79373.17969999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>77378.4375</v>
+        <v>77056.14840000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>78548.63280000001</v>
+        <v>77667.57030000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>67577.246</v>
+        <v>67281.43769999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>69425.39</v>
+        <v>69363.75599999999</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>30 aug</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>2417.9031</v>
+        <v>2457.6919</v>
       </c>
       <c r="BE21" t="n">
-        <v>2488.9229</v>
+        <v>2532.959</v>
       </c>
       <c r="BF21" t="n">
-        <v>2401.8088</v>
+        <v>2389.4692</v>
       </c>
       <c r="BG21" t="n">
-        <v>2466.8203</v>
+        <v>2417.9387</v>
       </c>
       <c r="BH21" t="n">
-        <v>2030.5757</v>
+        <v>2017.3551</v>
       </c>
       <c r="BI21" t="n">
-        <v>2025.2573</v>
+        <v>2022.6579</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -12178,7 +12190,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -12207,7 +12219,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC22" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -12257,49 +12269,49 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="AV22" t="n">
-        <v>78539.8594</v>
+        <v>77673.7031</v>
       </c>
       <c r="AW22" t="n">
-        <v>79196.5156</v>
+        <v>79247.3438</v>
       </c>
       <c r="AX22" t="n">
-        <v>76399.0625</v>
+        <v>77378.4375</v>
       </c>
       <c r="AY22" t="n">
-        <v>77403.625</v>
+        <v>78548.63280000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>67880.5361</v>
+        <v>67577.246</v>
       </c>
       <c r="BA22" t="n">
-        <v>69468.1189</v>
+        <v>69425.39</v>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2466.5752</v>
+        <v>2417.9031</v>
       </c>
       <c r="BE22" t="n">
-        <v>2484.3989</v>
+        <v>2488.9229</v>
       </c>
       <c r="BF22" t="n">
-        <v>2383.8037</v>
+        <v>2401.8088</v>
       </c>
       <c r="BG22" t="n">
-        <v>2417.842</v>
+        <v>2466.8203</v>
       </c>
       <c r="BH22" t="n">
-        <v>2043.4626</v>
+        <v>2030.5757</v>
       </c>
       <c r="BI22" t="n">
-        <v>2027.1038</v>
+        <v>2025.2573</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -12451,7 +12463,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -12480,7 +12492,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC23" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -12530,49 +12542,49 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="AV23" t="n">
-        <v>77402.1406</v>
+        <v>78539.8594</v>
       </c>
       <c r="AW23" t="n">
-        <v>77737.5469</v>
+        <v>79196.5156</v>
       </c>
       <c r="AX23" t="n">
-        <v>76248.30469999999</v>
+        <v>76399.0625</v>
       </c>
       <c r="AY23" t="n">
-        <v>77300.47659999999</v>
+        <v>77403.625</v>
       </c>
       <c r="AZ23" t="n">
-        <v>68127.4234</v>
+        <v>67880.5361</v>
       </c>
       <c r="BA23" t="n">
-        <v>69505.7831</v>
+        <v>69468.1189</v>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2417.8284</v>
+        <v>2466.5752</v>
       </c>
       <c r="BE23" t="n">
-        <v>2427.4016</v>
+        <v>2484.3989</v>
       </c>
       <c r="BF23" t="n">
-        <v>2356.1882</v>
+        <v>2383.8037</v>
       </c>
       <c r="BG23" t="n">
-        <v>2391.501</v>
+        <v>2417.842</v>
       </c>
       <c r="BH23" t="n">
-        <v>2053.503</v>
+        <v>2043.4626</v>
       </c>
       <c r="BI23" t="n">
-        <v>2028.6313</v>
+        <v>2027.1038</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -12724,7 +12736,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -12753,7 +12765,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC24" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -12803,49 +12815,49 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="AV24" t="n">
-        <v>77300.16409999999</v>
+        <v>77402.1406</v>
       </c>
       <c r="AW24" t="n">
-        <v>82262.21090000001</v>
+        <v>77737.5469</v>
       </c>
       <c r="AX24" t="n">
-        <v>76940.88280000001</v>
+        <v>76248.30469999999</v>
       </c>
       <c r="AY24" t="n">
-        <v>81271.74219999999</v>
+        <v>77300.47659999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>68458.6107</v>
+        <v>68127.4234</v>
       </c>
       <c r="BA24" t="n">
-        <v>69568.2009</v>
+        <v>69505.7831</v>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>2391.5999</v>
+        <v>2417.8284</v>
       </c>
       <c r="BE24" t="n">
-        <v>2526.9502</v>
+        <v>2427.4016</v>
       </c>
       <c r="BF24" t="n">
-        <v>2370.4155</v>
+        <v>2356.1882</v>
       </c>
       <c r="BG24" t="n">
-        <v>2508.0208</v>
+        <v>2391.501</v>
       </c>
       <c r="BH24" t="n">
-        <v>2065.3245</v>
+        <v>2053.503</v>
       </c>
       <c r="BI24" t="n">
-        <v>2031.3412</v>
+        <v>2028.6313</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -12997,7 +13009,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -13026,7 +13038,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC25" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -13076,49 +13088,49 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="AV25" t="n">
-        <v>81271.53909999999</v>
+        <v>77300.16409999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>81433.14840000001</v>
+        <v>82262.21090000001</v>
       </c>
       <c r="AX25" t="n">
-        <v>78641.625</v>
+        <v>76940.88280000001</v>
       </c>
       <c r="AY25" t="n">
-        <v>79671.9688</v>
+        <v>81271.74219999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>68776.2645</v>
+        <v>68458.6107</v>
       </c>
       <c r="BA25" t="n">
-        <v>69622.345</v>
+        <v>69568.2009</v>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>2508.0159</v>
+        <v>2391.5999</v>
       </c>
       <c r="BE25" t="n">
-        <v>2545.6235</v>
+        <v>2526.9502</v>
       </c>
       <c r="BF25" t="n">
-        <v>2432.3542</v>
+        <v>2370.4155</v>
       </c>
       <c r="BG25" t="n">
-        <v>2456.0781</v>
+        <v>2508.0208</v>
       </c>
       <c r="BH25" t="n">
-        <v>2077.1822</v>
+        <v>2065.3245</v>
       </c>
       <c r="BI25" t="n">
-        <v>2033.632</v>
+        <v>2031.3412</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -13270,7 +13282,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -13299,7 +13311,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC26" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -13349,49 +13361,49 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>5 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="AV26" t="n">
-        <v>79671.7031</v>
+        <v>81271.53909999999</v>
       </c>
       <c r="AW26" t="n">
-        <v>80194.50780000001</v>
+        <v>81433.14840000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>79465.0625</v>
+        <v>78641.625</v>
       </c>
       <c r="AY26" t="n">
-        <v>79823.86719999999</v>
+        <v>79671.9688</v>
       </c>
       <c r="AZ26" t="n">
-        <v>69094.75260000001</v>
+        <v>68776.2645</v>
       </c>
       <c r="BA26" t="n">
-        <v>69683.9932</v>
+        <v>69622.345</v>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>5 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>2455.988</v>
+        <v>2508.0159</v>
       </c>
       <c r="BE26" t="n">
-        <v>2492.0056</v>
+        <v>2545.6235</v>
       </c>
       <c r="BF26" t="n">
-        <v>2445.6858</v>
+        <v>2432.3542</v>
       </c>
       <c r="BG26" t="n">
-        <v>2480.7356</v>
+        <v>2456.0781</v>
       </c>
       <c r="BH26" t="n">
-        <v>2089.9772</v>
+        <v>2077.1822</v>
       </c>
       <c r="BI26" t="n">
-        <v>2036.0747</v>
+        <v>2033.632</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -13543,7 +13555,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -13572,7 +13584,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC27" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -13622,49 +13634,49 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>6 sep</t>
+          <t>5 sep</t>
         </is>
       </c>
       <c r="AV27" t="n">
-        <v>79824.60159999999</v>
+        <v>79671.7031</v>
       </c>
       <c r="AW27" t="n">
-        <v>80530.64840000001</v>
+        <v>80194.50780000001</v>
       </c>
       <c r="AX27" t="n">
-        <v>79327.5</v>
+        <v>79465.0625</v>
       </c>
       <c r="AY27" t="n">
-        <v>80350.0469</v>
+        <v>79823.86719999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>69405.82150000001</v>
+        <v>69094.75260000001</v>
       </c>
       <c r="BA27" t="n">
-        <v>69753.6168</v>
+        <v>69683.9932</v>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>6 sep</t>
+          <t>5 sep</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>2480.8247</v>
+        <v>2455.988</v>
       </c>
       <c r="BE27" t="n">
-        <v>2525.3215</v>
+        <v>2492.0056</v>
       </c>
       <c r="BF27" t="n">
-        <v>2468.1948</v>
+        <v>2445.6858</v>
       </c>
       <c r="BG27" t="n">
-        <v>2514.5488</v>
+        <v>2480.7356</v>
       </c>
       <c r="BH27" t="n">
-        <v>2103.0403</v>
+        <v>2089.9772</v>
       </c>
       <c r="BI27" t="n">
-        <v>2038.8776</v>
+        <v>2036.0747</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -13730,7 +13742,7 @@
         <v>936.9625</v>
       </c>
       <c r="CF27" t="n">
-        <v>962.1174</v>
+        <v>962.1174999999999</v>
       </c>
       <c r="CG27" t="n">
         <v>563.4435999999999</v>
@@ -13816,7 +13828,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -13845,7 +13857,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC28" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -13895,49 +13907,49 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>6 sep</t>
         </is>
       </c>
       <c r="AV28" t="n">
-        <v>80349.19530000001</v>
+        <v>79824.60159999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>80432.3125</v>
+        <v>80530.64840000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>78684.92969999999</v>
+        <v>79327.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>79115.85159999999</v>
+        <v>80350.0469</v>
       </c>
       <c r="AZ28" t="n">
-        <v>69694.3224</v>
+        <v>69405.82150000001</v>
       </c>
       <c r="BA28" t="n">
-        <v>69814.40850000001</v>
+        <v>69753.6168</v>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>6 sep</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>2514.583</v>
+        <v>2480.8247</v>
       </c>
       <c r="BE28" t="n">
-        <v>2534.8618</v>
+        <v>2525.3215</v>
       </c>
       <c r="BF28" t="n">
-        <v>2466.9131</v>
+        <v>2468.1948</v>
       </c>
       <c r="BG28" t="n">
-        <v>2490.958</v>
+        <v>2514.5488</v>
       </c>
       <c r="BH28" t="n">
-        <v>2115.4293</v>
+        <v>2103.0403</v>
       </c>
       <c r="BI28" t="n">
-        <v>2041.5913</v>
+        <v>2038.8776</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -14089,7 +14101,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -14118,7 +14130,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC29" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -14168,49 +14180,49 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="AV29" t="n">
-        <v>79114.9062</v>
+        <v>80349.19530000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>79463.27340000001</v>
+        <v>80432.3125</v>
       </c>
       <c r="AX29" t="n">
-        <v>77635.6875</v>
+        <v>78684.92969999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>78438.5781</v>
+        <v>79115.85159999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>69958.49340000001</v>
+        <v>69694.3224</v>
       </c>
       <c r="BA29" t="n">
-        <v>69866.57429999999</v>
+        <v>69814.40850000001</v>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>2490.9197</v>
+        <v>2514.583</v>
       </c>
       <c r="BE29" t="n">
-        <v>2506.7532</v>
+        <v>2534.8618</v>
       </c>
       <c r="BF29" t="n">
-        <v>2441.3289</v>
+        <v>2466.9131</v>
       </c>
       <c r="BG29" t="n">
-        <v>2484.9414</v>
+        <v>2490.958</v>
       </c>
       <c r="BH29" t="n">
-        <v>2127.0529</v>
+        <v>2115.4293</v>
       </c>
       <c r="BI29" t="n">
-        <v>2044.1709</v>
+        <v>2041.5913</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -14327,7 +14339,7 @@
         <v>421.046</v>
       </c>
       <c r="G30" t="n">
-        <v>429.3186</v>
+        <v>429.3185</v>
       </c>
       <c r="H30" t="n">
         <v>535.3375423278808</v>
@@ -14362,7 +14374,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -14391,7 +14403,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC30" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -14441,49 +14453,49 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="AV30" t="n">
-        <v>78440.60159999999</v>
+        <v>79114.9062</v>
       </c>
       <c r="AW30" t="n">
-        <v>79737.2969</v>
+        <v>79463.27340000001</v>
       </c>
       <c r="AX30" t="n">
-        <v>77768.14840000001</v>
+        <v>77635.6875</v>
       </c>
       <c r="AY30" t="n">
-        <v>78259.52340000001</v>
+        <v>78438.5781</v>
       </c>
       <c r="AZ30" t="n">
-        <v>70193.5814</v>
+        <v>69958.49340000001</v>
       </c>
       <c r="BA30" t="n">
-        <v>69917.853</v>
+        <v>69866.57429999999</v>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>2484.8943</v>
+        <v>2490.9197</v>
       </c>
       <c r="BE30" t="n">
-        <v>2522.3696</v>
+        <v>2506.7532</v>
       </c>
       <c r="BF30" t="n">
-        <v>2443.7024</v>
+        <v>2441.3289</v>
       </c>
       <c r="BG30" t="n">
-        <v>2466.9138</v>
+        <v>2484.9414</v>
       </c>
       <c r="BH30" t="n">
-        <v>2137.8235</v>
+        <v>2127.0529</v>
       </c>
       <c r="BI30" t="n">
-        <v>2046.6368</v>
+        <v>2044.1709</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -14635,7 +14647,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -14664,7 +14676,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC31" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -14714,49 +14726,49 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="AV31" t="n">
-        <v>78260.38280000001</v>
+        <v>78440.60159999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>78520.9688</v>
+        <v>79737.2969</v>
       </c>
       <c r="AX31" t="n">
-        <v>76470.6406</v>
+        <v>77768.14840000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>76568.125</v>
+        <v>78259.52340000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>70402.928</v>
+        <v>70193.5814</v>
       </c>
       <c r="BA31" t="n">
-        <v>69962.3967</v>
+        <v>69917.853</v>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>2466.9131</v>
+        <v>2484.8943</v>
       </c>
       <c r="BE31" t="n">
-        <v>2483.72</v>
+        <v>2522.3696</v>
       </c>
       <c r="BF31" t="n">
-        <v>2406.9065</v>
+        <v>2443.7024</v>
       </c>
       <c r="BG31" t="n">
-        <v>2437.0986</v>
+        <v>2466.9138</v>
       </c>
       <c r="BH31" t="n">
-        <v>2147.8957</v>
+        <v>2137.8235</v>
       </c>
       <c r="BI31" t="n">
-        <v>2049.0333</v>
+        <v>2046.6368</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -14908,7 +14920,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -14937,7 +14949,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC32" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -14987,49 +14999,49 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="AV32" t="n">
-        <v>76559.125</v>
+        <v>78260.38280000001</v>
       </c>
       <c r="AW32" t="n">
-        <v>79818.33590000001</v>
+        <v>78520.9688</v>
       </c>
       <c r="AX32" t="n">
-        <v>76162.91409999999</v>
+        <v>76470.6406</v>
       </c>
       <c r="AY32" t="n">
-        <v>77173.7969</v>
+        <v>76568.125</v>
       </c>
       <c r="AZ32" t="n">
-        <v>70645.5077</v>
+        <v>70402.928</v>
       </c>
       <c r="BA32" t="n">
-        <v>70025.182</v>
+        <v>69962.3967</v>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="BD32" t="n">
-        <v>2437.1357</v>
+        <v>2466.9131</v>
       </c>
       <c r="BE32" t="n">
-        <v>2663.0503</v>
+        <v>2483.72</v>
       </c>
       <c r="BF32" t="n">
-        <v>2435.2854</v>
+        <v>2406.9065</v>
       </c>
       <c r="BG32" t="n">
-        <v>2514.7339</v>
+        <v>2437.0986</v>
       </c>
       <c r="BH32" t="n">
-        <v>2160.6484</v>
+        <v>2147.8957</v>
       </c>
       <c r="BI32" t="n">
-        <v>2052.3294</v>
+        <v>2049.0333</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -15181,7 +15193,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -15210,7 +15222,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC33" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -15260,49 +15272,49 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>12 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="AV33" t="n">
-        <v>77175.07030000001</v>
+        <v>76559.125</v>
       </c>
       <c r="AW33" t="n">
-        <v>77479.6562</v>
+        <v>79818.33590000001</v>
       </c>
       <c r="AX33" t="n">
-        <v>77045</v>
+        <v>76162.91409999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>77270.4688</v>
+        <v>77173.7969</v>
       </c>
       <c r="AZ33" t="n">
-        <v>70908.9471</v>
+        <v>70645.5077</v>
       </c>
       <c r="BA33" t="n">
-        <v>70091.1341</v>
+        <v>70025.182</v>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>12 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="BD33" t="n">
-        <v>2514.77</v>
+        <v>2437.1357</v>
       </c>
       <c r="BE33" t="n">
-        <v>2544.4724</v>
+        <v>2663.0503</v>
       </c>
       <c r="BF33" t="n">
-        <v>2508.8015</v>
+        <v>2435.2854</v>
       </c>
       <c r="BG33" t="n">
-        <v>2525.9446</v>
+        <v>2514.7339</v>
       </c>
       <c r="BH33" t="n">
-        <v>2173.9637</v>
+        <v>2160.6484</v>
       </c>
       <c r="BI33" t="n">
-        <v>2055.6943</v>
+        <v>2052.3294</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
@@ -15454,7 +15466,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -15483,7 +15495,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC34" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -15533,49 +15545,49 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>13 sep</t>
+          <t>12 sep</t>
         </is>
       </c>
       <c r="AV34" t="n">
-        <v>77270.17969999999</v>
+        <v>77175.07030000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>77415.6562</v>
+        <v>77479.6562</v>
       </c>
       <c r="AX34" t="n">
-        <v>76498.38280000001</v>
+        <v>77045</v>
       </c>
       <c r="AY34" t="n">
-        <v>76838.1562</v>
+        <v>77270.4688</v>
       </c>
       <c r="AZ34" t="n">
-        <v>71159.474</v>
+        <v>70908.9471</v>
       </c>
       <c r="BA34" t="n">
-        <v>70135.5243</v>
+        <v>70091.1341</v>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>13 sep</t>
+          <t>12 sep</t>
         </is>
       </c>
       <c r="BD34" t="n">
-        <v>2525.9424</v>
+        <v>2514.77</v>
       </c>
       <c r="BE34" t="n">
-        <v>2526.8538</v>
+        <v>2544.4724</v>
       </c>
       <c r="BF34" t="n">
-        <v>2462.8396</v>
+        <v>2508.8015</v>
       </c>
       <c r="BG34" t="n">
-        <v>2477.0208</v>
+        <v>2525.9446</v>
       </c>
       <c r="BH34" t="n">
-        <v>2186.0397</v>
+        <v>2173.9637</v>
       </c>
       <c r="BI34" t="n">
-        <v>2057.8063</v>
+        <v>2055.6943</v>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
@@ -15727,7 +15739,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -15756,7 +15768,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC35" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -15806,49 +15818,49 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>13 sep</t>
         </is>
       </c>
       <c r="AV35" t="n">
-        <v>76830.2812</v>
+        <v>77270.17969999999</v>
       </c>
       <c r="AW35" t="n">
-        <v>79568.9531</v>
+        <v>77415.6562</v>
       </c>
       <c r="AX35" t="n">
-        <v>76367.375</v>
+        <v>76498.38280000001</v>
       </c>
       <c r="AY35" t="n">
-        <v>78163.38280000001</v>
+        <v>76838.1562</v>
       </c>
       <c r="AZ35" t="n">
-        <v>71415.9356</v>
+        <v>71159.474</v>
       </c>
       <c r="BA35" t="n">
-        <v>70189.0723</v>
+        <v>70135.5243</v>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>13 sep</t>
         </is>
       </c>
       <c r="BD35" t="n">
-        <v>2476.603</v>
+        <v>2525.9424</v>
       </c>
       <c r="BE35" t="n">
-        <v>2612.4033</v>
+        <v>2526.8538</v>
       </c>
       <c r="BF35" t="n">
-        <v>2465.4265</v>
+        <v>2462.8396</v>
       </c>
       <c r="BG35" t="n">
-        <v>2514.407</v>
+        <v>2477.0208</v>
       </c>
       <c r="BH35" t="n">
-        <v>2197.2596</v>
+        <v>2186.0397</v>
       </c>
       <c r="BI35" t="n">
-        <v>2060.2444</v>
+        <v>2057.8063</v>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
@@ -16000,7 +16012,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -16029,7 +16041,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC36" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -16079,49 +16091,49 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="AV36" t="n">
-        <v>78162.4844</v>
+        <v>76830.2812</v>
       </c>
       <c r="AW36" t="n">
-        <v>78242.5469</v>
+        <v>79568.9531</v>
       </c>
       <c r="AX36" t="n">
-        <v>74944.5938</v>
+        <v>76367.375</v>
       </c>
       <c r="AY36" t="n">
-        <v>75612.50780000001</v>
+        <v>78163.38280000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>71653.6878</v>
+        <v>71415.9356</v>
       </c>
       <c r="BA36" t="n">
-        <v>70237.7259</v>
+        <v>70189.0723</v>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="BD36" t="n">
-        <v>2514.3618</v>
+        <v>2476.603</v>
       </c>
       <c r="BE36" t="n">
-        <v>2519.3188</v>
+        <v>2612.4033</v>
       </c>
       <c r="BF36" t="n">
-        <v>2357.9592</v>
+        <v>2465.4265</v>
       </c>
       <c r="BG36" t="n">
-        <v>2399.0869</v>
+        <v>2514.407</v>
       </c>
       <c r="BH36" t="n">
-        <v>2207.4291</v>
+        <v>2197.2596</v>
       </c>
       <c r="BI36" t="n">
-        <v>2062.586</v>
+        <v>2060.2444</v>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
@@ -16273,7 +16285,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -16302,7 +16314,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC37" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -16352,49 +16364,49 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="AV37" t="n">
-        <v>75611.7969</v>
+        <v>78162.4844</v>
       </c>
       <c r="AW37" t="n">
-        <v>76474.0781</v>
+        <v>78242.5469</v>
       </c>
       <c r="AX37" t="n">
-        <v>74995.52340000001</v>
+        <v>74944.5938</v>
       </c>
       <c r="AY37" t="n">
-        <v>76150.32030000001</v>
+        <v>75612.50780000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>71899.26700000001</v>
+        <v>71653.6878</v>
       </c>
       <c r="BA37" t="n">
-        <v>70283.4982</v>
+        <v>70237.7259</v>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="BD37" t="n">
-        <v>2399.0554</v>
+        <v>2514.3618</v>
       </c>
       <c r="BE37" t="n">
-        <v>2426.9294</v>
+        <v>2519.3188</v>
       </c>
       <c r="BF37" t="n">
-        <v>2368.7358</v>
+        <v>2357.9592</v>
       </c>
       <c r="BG37" t="n">
-        <v>2416.1199</v>
+        <v>2399.0869</v>
       </c>
       <c r="BH37" t="n">
-        <v>2217.3525</v>
+        <v>2207.4291</v>
       </c>
       <c r="BI37" t="n">
-        <v>2064.8413</v>
+        <v>2062.586</v>
       </c>
       <c r="BK37" t="inlineStr">
         <is>
@@ -16546,7 +16558,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -16575,7 +16587,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC38" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -16625,49 +16637,49 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="AV38" t="n">
-        <v>76152.05469999999</v>
+        <v>75611.7969</v>
       </c>
       <c r="AW38" t="n">
-        <v>77079.16409999999</v>
+        <v>76474.0781</v>
       </c>
       <c r="AX38" t="n">
-        <v>75945.55469999999</v>
+        <v>74995.52340000001</v>
       </c>
       <c r="AY38" t="n">
-        <v>76403.77340000001</v>
+        <v>76150.32030000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>72149.17909999999</v>
+        <v>71899.26700000001</v>
       </c>
       <c r="BA38" t="n">
-        <v>70336.8266</v>
+        <v>70283.4982</v>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="BD38" t="n">
-        <v>2416.1677</v>
+        <v>2399.0554</v>
       </c>
       <c r="BE38" t="n">
-        <v>2480.7371</v>
+        <v>2426.9294</v>
       </c>
       <c r="BF38" t="n">
-        <v>2412.1877</v>
+        <v>2368.7358</v>
       </c>
       <c r="BG38" t="n">
-        <v>2447.1067</v>
+        <v>2416.1199</v>
       </c>
       <c r="BH38" t="n">
-        <v>2228.1243</v>
+        <v>2217.3525</v>
       </c>
       <c r="BI38" t="n">
-        <v>2067.3815</v>
+        <v>2064.8413</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -16819,7 +16831,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -16848,7 +16860,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC39" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -16898,49 +16910,49 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="AV39" t="n">
-        <v>76405.0156</v>
+        <v>76152.05469999999</v>
       </c>
       <c r="AW39" t="n">
-        <v>81331.7656</v>
+        <v>77079.16409999999</v>
       </c>
       <c r="AX39" t="n">
-        <v>76228.3281</v>
+        <v>75945.55469999999</v>
       </c>
       <c r="AY39" t="n">
-        <v>80901.46090000001</v>
+        <v>76403.77340000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>72472.70209999999</v>
+        <v>72149.17909999999</v>
       </c>
       <c r="BA39" t="n">
-        <v>70397.4546</v>
+        <v>70336.8266</v>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="BD39" t="n">
+        <v>2416.1677</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>2480.7371</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>2412.1877</v>
+      </c>
+      <c r="BG39" t="n">
         <v>2447.1067</v>
       </c>
-      <c r="BE39" t="n">
-        <v>2643.9622</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>2435.1484</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>2611.3472</v>
-      </c>
       <c r="BH39" t="n">
-        <v>2242.0038</v>
+        <v>2228.1243</v>
       </c>
       <c r="BI39" t="n">
-        <v>2070.3019</v>
+        <v>2067.3815</v>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
@@ -17092,7 +17104,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -17121,7 +17133,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC40" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -17171,49 +17183,49 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>19 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="AV40" t="n">
-        <v>80900.28909999999</v>
+        <v>76405.0156</v>
       </c>
       <c r="AW40" t="n">
-        <v>81911.1406</v>
+        <v>81331.7656</v>
       </c>
       <c r="AX40" t="n">
-        <v>80814.9375</v>
+        <v>76228.3281</v>
       </c>
       <c r="AY40" t="n">
-        <v>81233.67969999999</v>
+        <v>80901.46090000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>72841.1008</v>
+        <v>72472.70209999999</v>
       </c>
       <c r="BA40" t="n">
-        <v>70462.1548</v>
+        <v>70397.4546</v>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>19 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="BD40" t="n">
-        <v>2611.4563</v>
+        <v>2447.1067</v>
       </c>
       <c r="BE40" t="n">
-        <v>2659.7183</v>
+        <v>2643.9622</v>
       </c>
       <c r="BF40" t="n">
-        <v>2602.7368</v>
+        <v>2435.1484</v>
       </c>
       <c r="BG40" t="n">
-        <v>2631.9626</v>
+        <v>2611.3472</v>
       </c>
       <c r="BH40" t="n">
-        <v>2257.4361</v>
+        <v>2242.0038</v>
       </c>
       <c r="BI40" t="n">
-        <v>2073.5479</v>
+        <v>2070.3019</v>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
@@ -17365,7 +17377,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -17394,7 +17406,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC41" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -17444,49 +17456,49 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>20 sep</t>
+          <t>19 sep</t>
         </is>
       </c>
       <c r="AV41" t="n">
-        <v>81234.30469999999</v>
+        <v>80900.28909999999</v>
       </c>
       <c r="AW41" t="n">
-        <v>81455.2031</v>
+        <v>81911.1406</v>
       </c>
       <c r="AX41" t="n">
-        <v>80098.77340000001</v>
+        <v>80814.9375</v>
       </c>
       <c r="AY41" t="n">
-        <v>81142.6094</v>
+        <v>81233.67969999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>73208.6866</v>
+        <v>72841.1008</v>
       </c>
       <c r="BA41" t="n">
-        <v>70504.3149</v>
+        <v>70462.1548</v>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>20 sep</t>
+          <t>19 sep</t>
         </is>
       </c>
       <c r="BD41" t="n">
-        <v>2632.0146</v>
+        <v>2611.4563</v>
       </c>
       <c r="BE41" t="n">
-        <v>2647.8735</v>
+        <v>2659.7183</v>
       </c>
       <c r="BF41" t="n">
-        <v>2564.4326</v>
+        <v>2602.7368</v>
       </c>
       <c r="BG41" t="n">
-        <v>2642.9976</v>
+        <v>2631.9626</v>
       </c>
       <c r="BH41" t="n">
-        <v>2273.4277</v>
+        <v>2257.4361</v>
       </c>
       <c r="BI41" t="n">
-        <v>2076.1303</v>
+        <v>2073.5479</v>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
@@ -17638,7 +17650,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -17667,7 +17679,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC42" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -17717,49 +17729,49 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>20 sep</t>
         </is>
       </c>
       <c r="AV42" t="n">
-        <v>81143.625</v>
+        <v>81234.30469999999</v>
       </c>
       <c r="AW42" t="n">
-        <v>87363.75780000001</v>
+        <v>81455.2031</v>
       </c>
       <c r="AX42" t="n">
-        <v>80867.08590000001</v>
+        <v>80098.77340000001</v>
       </c>
       <c r="AY42" t="n">
-        <v>86602.91409999999</v>
+        <v>81142.6094</v>
       </c>
       <c r="AZ42" t="n">
-        <v>73671.1048</v>
+        <v>73208.6866</v>
       </c>
       <c r="BA42" t="n">
-        <v>70583.12390000001</v>
+        <v>70504.3149</v>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>20 sep</t>
         </is>
       </c>
       <c r="BD42" t="n">
-        <v>2642.7822</v>
+        <v>2632.0146</v>
       </c>
       <c r="BE42" t="n">
-        <v>2805.499</v>
+        <v>2647.8735</v>
       </c>
       <c r="BF42" t="n">
-        <v>2642.7822</v>
+        <v>2564.4326</v>
       </c>
       <c r="BG42" t="n">
-        <v>2776.4683</v>
+        <v>2642.9976</v>
       </c>
       <c r="BH42" t="n">
-        <v>2291.3066</v>
+        <v>2273.4277</v>
       </c>
       <c r="BI42" t="n">
-        <v>2079.6547</v>
+        <v>2076.1303</v>
       </c>
       <c r="BK42" t="inlineStr">
         <is>
@@ -17876,7 +17888,7 @@
         <v>453.115</v>
       </c>
       <c r="G43" t="n">
-        <v>429.654</v>
+        <v>429.6539</v>
       </c>
       <c r="H43" t="n">
         <v>535.3375423278808</v>
@@ -17911,7 +17923,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -17940,7 +17952,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC43" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -17990,49 +18002,49 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="AV43" t="n">
-        <v>86604.375</v>
+        <v>81143.625</v>
       </c>
       <c r="AW43" t="n">
-        <v>86700</v>
+        <v>87363.75780000001</v>
       </c>
       <c r="AX43" t="n">
-        <v>85098.00780000001</v>
+        <v>80867.08590000001</v>
       </c>
       <c r="AY43" t="n">
-        <v>86172.2812</v>
+        <v>86602.91409999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>74125.3325</v>
+        <v>73671.1048</v>
       </c>
       <c r="BA43" t="n">
-        <v>70673.3028</v>
+        <v>70583.12390000001</v>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="BD43" t="n">
-        <v>2776.5803</v>
+        <v>2642.7822</v>
       </c>
       <c r="BE43" t="n">
-        <v>2776.8889</v>
+        <v>2805.499</v>
       </c>
       <c r="BF43" t="n">
-        <v>2715.7156</v>
+        <v>2642.7822</v>
       </c>
       <c r="BG43" t="n">
-        <v>2752.6326</v>
+        <v>2776.4683</v>
       </c>
       <c r="BH43" t="n">
-        <v>2309.1941</v>
+        <v>2291.3066</v>
       </c>
       <c r="BI43" t="n">
-        <v>2083.5241</v>
+        <v>2079.6547</v>
       </c>
       <c r="BK43" t="inlineStr">
         <is>
@@ -18184,7 +18196,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -18213,7 +18225,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC44" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -18263,49 +18275,49 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="AV44" t="n">
-        <v>86176.7656</v>
+        <v>86604.375</v>
       </c>
       <c r="AW44" t="n">
-        <v>87265.49219999999</v>
+        <v>86700</v>
       </c>
       <c r="AX44" t="n">
-        <v>83519.7344</v>
+        <v>85098.00780000001</v>
       </c>
       <c r="AY44" t="n">
-        <v>84383.00780000001</v>
+        <v>86172.2812</v>
       </c>
       <c r="AZ44" t="n">
-        <v>74531.87360000001</v>
+        <v>74125.3325</v>
       </c>
       <c r="BA44" t="n">
-        <v>70758.85490000001</v>
+        <v>70673.3028</v>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="BD44" t="n">
-        <v>2752.7524</v>
+        <v>2776.5803</v>
       </c>
       <c r="BE44" t="n">
-        <v>2787.9626</v>
+        <v>2776.8889</v>
       </c>
       <c r="BF44" t="n">
-        <v>2636.9131</v>
+        <v>2715.7156</v>
       </c>
       <c r="BG44" t="n">
-        <v>2684.6919</v>
+        <v>2752.6326</v>
       </c>
       <c r="BH44" t="n">
-        <v>2325.5203</v>
+        <v>2309.1941</v>
       </c>
       <c r="BI44" t="n">
-        <v>2087.1002</v>
+        <v>2083.5241</v>
       </c>
       <c r="BK44" t="inlineStr">
         <is>
@@ -18457,7 +18469,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -18486,7 +18498,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC45" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -18532,53 +18544,53 @@
         <v>1502.867</v>
       </c>
       <c r="AS45" t="n">
-        <v>1301.1271</v>
+        <v>1301.1272</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="AV45" t="n">
-        <v>84381.5938</v>
+        <v>86176.7656</v>
       </c>
       <c r="AW45" t="n">
-        <v>84876.22659999999</v>
+        <v>87265.49219999999</v>
       </c>
       <c r="AX45" t="n">
-        <v>82906.61719999999</v>
+        <v>83519.7344</v>
       </c>
       <c r="AY45" t="n">
-        <v>84379.0625</v>
+        <v>84383.00780000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>74927.5048</v>
+        <v>74531.87360000001</v>
       </c>
       <c r="BA45" t="n">
-        <v>70850.9013</v>
+        <v>70758.85490000001</v>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="BD45" t="n">
-        <v>2684.4395</v>
+        <v>2752.7524</v>
       </c>
       <c r="BE45" t="n">
-        <v>2703.6628</v>
+        <v>2787.9626</v>
       </c>
       <c r="BF45" t="n">
-        <v>2628.6892</v>
+        <v>2636.9131</v>
       </c>
       <c r="BG45" t="n">
-        <v>2687.3015</v>
+        <v>2684.6919</v>
       </c>
       <c r="BH45" t="n">
-        <v>2341.1358</v>
+        <v>2325.5203</v>
       </c>
       <c r="BI45" t="n">
-        <v>2090.8537</v>
+        <v>2087.1002</v>
       </c>
       <c r="BK45" t="inlineStr">
         <is>
@@ -18730,7 +18742,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -18759,7 +18771,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC46" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -18809,49 +18821,49 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="AV46" t="n">
-        <v>84379.5156</v>
+        <v>84381.5938</v>
       </c>
       <c r="AW46" t="n">
-        <v>85230.05469999999</v>
+        <v>84876.22659999999</v>
       </c>
       <c r="AX46" t="n">
-        <v>83165.5312</v>
+        <v>82906.61719999999</v>
       </c>
       <c r="AY46" t="n">
-        <v>84034.9219</v>
+        <v>84379.0625</v>
       </c>
       <c r="AZ46" t="n">
-        <v>75322.961</v>
+        <v>74927.5048</v>
       </c>
       <c r="BA46" t="n">
-        <v>70929.064</v>
+        <v>70850.9013</v>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="BD46" t="n">
-        <v>2687.3225</v>
+        <v>2684.4395</v>
       </c>
       <c r="BE46" t="n">
-        <v>2741.2969</v>
+        <v>2703.6628</v>
       </c>
       <c r="BF46" t="n">
-        <v>2667.0452</v>
+        <v>2628.6892</v>
       </c>
       <c r="BG46" t="n">
-        <v>2690.4756</v>
+        <v>2687.3015</v>
       </c>
       <c r="BH46" t="n">
-        <v>2356.9041</v>
+        <v>2341.1358</v>
       </c>
       <c r="BI46" t="n">
-        <v>2094.3414</v>
+        <v>2090.8537</v>
       </c>
       <c r="BK46" t="inlineStr">
         <is>
@@ -19003,7 +19015,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -19032,7 +19044,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC47" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -19082,49 +19094,49 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>26 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="AV47" t="n">
-        <v>84035.82030000001</v>
+        <v>84379.5156</v>
       </c>
       <c r="AW47" t="n">
-        <v>84423.17969999999</v>
+        <v>85230.05469999999</v>
       </c>
       <c r="AX47" t="n">
-        <v>83781.1094</v>
+        <v>83165.5312</v>
       </c>
       <c r="AY47" t="n">
-        <v>84406.4531</v>
+        <v>84034.9219</v>
       </c>
       <c r="AZ47" t="n">
-        <v>75713.4863</v>
+        <v>75322.961</v>
       </c>
       <c r="BA47" t="n">
-        <v>71001.4616</v>
+        <v>70929.064</v>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>26 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="BD47" t="n">
-        <v>2690.4817</v>
+        <v>2687.3225</v>
       </c>
       <c r="BE47" t="n">
-        <v>2696.9961</v>
+        <v>2741.2969</v>
       </c>
       <c r="BF47" t="n">
-        <v>2665.8625</v>
+        <v>2667.0452</v>
       </c>
       <c r="BG47" t="n">
-        <v>2695.2131</v>
+        <v>2690.4756</v>
       </c>
       <c r="BH47" t="n">
-        <v>2372.5428</v>
+        <v>2356.9041</v>
       </c>
       <c r="BI47" t="n">
-        <v>2097.6319</v>
+        <v>2094.3414</v>
       </c>
       <c r="BK47" t="inlineStr">
         <is>
@@ -19276,7 +19288,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -19305,7 +19317,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC48" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -19355,49 +19367,49 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>27 sep</t>
+          <t>26 sep</t>
         </is>
       </c>
       <c r="AV48" t="n">
-        <v>84412.7188</v>
+        <v>84035.82030000001</v>
       </c>
       <c r="AW48" t="n">
-        <v>85126.1094</v>
+        <v>84423.17969999999</v>
       </c>
       <c r="AX48" t="n">
-        <v>84121.3281</v>
+        <v>83781.1094</v>
       </c>
       <c r="AY48" t="n">
-        <v>84458.08590000001</v>
+        <v>84406.4531</v>
       </c>
       <c r="AZ48" t="n">
-        <v>76104.5542</v>
+        <v>75713.4863</v>
       </c>
       <c r="BA48" t="n">
-        <v>71072.7277</v>
+        <v>71001.4616</v>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>27 sep</t>
+          <t>26 sep</t>
         </is>
       </c>
       <c r="BD48" t="n">
-        <v>2695.3489</v>
+        <v>2690.4817</v>
       </c>
       <c r="BE48" t="n">
-        <v>2722.0393</v>
+        <v>2696.9961</v>
       </c>
       <c r="BF48" t="n">
-        <v>2669.4727</v>
+        <v>2665.8625</v>
       </c>
       <c r="BG48" t="n">
-        <v>2686.9268</v>
+        <v>2695.2131</v>
       </c>
       <c r="BH48" t="n">
-        <v>2387.9707</v>
+        <v>2372.5428</v>
       </c>
       <c r="BI48" t="n">
-        <v>2100.8087</v>
+        <v>2097.6319</v>
       </c>
       <c r="BK48" t="inlineStr">
         <is>
@@ -19549,7 +19561,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -19578,7 +19590,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC49" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -19628,49 +19640,49 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>27 sep</t>
         </is>
       </c>
       <c r="AV49" t="n">
-        <v>84454.11719999999</v>
+        <v>84412.7188</v>
       </c>
       <c r="AW49" t="n">
-        <v>84972.66409999999</v>
+        <v>85126.1094</v>
       </c>
       <c r="AX49" t="n">
-        <v>82570.7188</v>
+        <v>84121.3281</v>
       </c>
       <c r="AY49" t="n">
-        <v>83502.6094</v>
+        <v>84458.08590000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>76477.7087</v>
+        <v>76104.5542</v>
       </c>
       <c r="BA49" t="n">
-        <v>71137.77340000001</v>
+        <v>71072.7277</v>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>27 sep</t>
         </is>
       </c>
       <c r="BD49" t="n">
-        <v>2687.0007</v>
+        <v>2695.3489</v>
       </c>
       <c r="BE49" t="n">
-        <v>2718.8086</v>
+        <v>2722.0393</v>
       </c>
       <c r="BF49" t="n">
-        <v>2635.4846</v>
+        <v>2669.4727</v>
       </c>
       <c r="BG49" t="n">
-        <v>2688.6687</v>
+        <v>2686.9268</v>
       </c>
       <c r="BH49" t="n">
-        <v>2403.5704</v>
+        <v>2387.9707</v>
       </c>
       <c r="BI49" t="n">
-        <v>2103.8863</v>
+        <v>2100.8087</v>
       </c>
       <c r="BK49" t="inlineStr">
         <is>
@@ -19822,7 +19834,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -19851,7 +19863,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC50" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -19901,49 +19913,49 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="AV50" t="n">
-        <v>83500.32030000001</v>
+        <v>84454.11719999999</v>
       </c>
       <c r="AW50" t="n">
-        <v>84511.2812</v>
+        <v>84972.66409999999</v>
       </c>
       <c r="AX50" t="n">
-        <v>82739.0938</v>
+        <v>82570.7188</v>
       </c>
       <c r="AY50" t="n">
-        <v>83622.42969999999</v>
+        <v>83502.6094</v>
       </c>
       <c r="AZ50" t="n">
-        <v>76871.9455</v>
+        <v>76477.7087</v>
       </c>
       <c r="BA50" t="n">
-        <v>71201.0442</v>
+        <v>71137.77340000001</v>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="BD50" t="n">
-        <v>2688.634</v>
+        <v>2687.0007</v>
       </c>
       <c r="BE50" t="n">
-        <v>2746.0107</v>
+        <v>2718.8086</v>
       </c>
       <c r="BF50" t="n">
-        <v>2651.4714</v>
+        <v>2635.4846</v>
       </c>
       <c r="BG50" t="n">
-        <v>2676.7222</v>
+        <v>2688.6687</v>
       </c>
       <c r="BH50" t="n">
-        <v>2419.6793</v>
+        <v>2403.5704</v>
       </c>
       <c r="BI50" t="n">
-        <v>2106.8071</v>
+        <v>2103.8863</v>
       </c>
       <c r="BK50" t="inlineStr">
         <is>
@@ -20095,7 +20107,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -20124,7 +20136,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC51" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -20174,49 +20186,49 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="AV51" t="n">
-        <v>83621.39840000001</v>
+        <v>83500.32030000001</v>
       </c>
       <c r="AW51" t="n">
-        <v>85599.80469999999</v>
+        <v>84511.2812</v>
       </c>
       <c r="AX51" t="n">
-        <v>82927.875</v>
+        <v>82739.0938</v>
       </c>
       <c r="AY51" t="n">
-        <v>83553.85159999999</v>
+        <v>83622.42969999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>77271.98510000001</v>
+        <v>76871.9455</v>
       </c>
       <c r="BA51" t="n">
-        <v>71262.7404</v>
+        <v>71201.0442</v>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="BD51" t="n">
-        <v>2676.6921</v>
+        <v>2688.634</v>
       </c>
       <c r="BE51" t="n">
-        <v>2737.2649</v>
+        <v>2746.0107</v>
       </c>
       <c r="BF51" t="n">
-        <v>2657.0854</v>
+        <v>2651.4714</v>
       </c>
       <c r="BG51" t="n">
-        <v>2683.6794</v>
+        <v>2676.7222</v>
       </c>
       <c r="BH51" t="n">
-        <v>2435.7254</v>
+        <v>2419.6793</v>
       </c>
       <c r="BI51" t="n">
-        <v>2109.7401</v>
+        <v>2106.8071</v>
       </c>
       <c r="BK51" t="inlineStr">
         <is>
@@ -20368,7 +20380,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -20397,7 +20409,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC52" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -20447,49 +20459,49 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="AV52" t="n">
-        <v>83554.25</v>
+        <v>83621.39840000001</v>
       </c>
       <c r="AW52" t="n">
-        <v>85224.27340000001</v>
+        <v>85599.80469999999</v>
       </c>
       <c r="AX52" t="n">
-        <v>83132.75780000001</v>
+        <v>82927.875</v>
       </c>
       <c r="AY52" t="n">
-        <v>84853.10159999999</v>
+        <v>83553.85159999999</v>
       </c>
       <c r="AZ52" t="n">
-        <v>77700.9984</v>
+        <v>77271.98510000001</v>
       </c>
       <c r="BA52" t="n">
-        <v>71323.0563</v>
+        <v>71262.7404</v>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="BD52" t="n">
-        <v>2683.8191</v>
+        <v>2676.6921</v>
       </c>
       <c r="BE52" t="n">
-        <v>2720.188</v>
+        <v>2737.2649</v>
       </c>
       <c r="BF52" t="n">
-        <v>2672.7065</v>
+        <v>2657.0854</v>
       </c>
       <c r="BG52" t="n">
-        <v>2705.5371</v>
+        <v>2683.6794</v>
       </c>
       <c r="BH52" t="n">
-        <v>2452.2734</v>
+        <v>2435.7254</v>
       </c>
       <c r="BI52" t="n">
-        <v>2112.3804</v>
+        <v>2109.7401</v>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
@@ -20641,7 +20653,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -20670,7 +20682,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC53" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -20720,49 +20732,49 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="AV53" t="n">
-        <v>84855.64840000001</v>
+        <v>83554.25</v>
       </c>
       <c r="AW53" t="n">
-        <v>87146.35159999999</v>
+        <v>85224.27340000001</v>
       </c>
       <c r="AX53" t="n">
-        <v>83852.69530000001</v>
+        <v>83132.75780000001</v>
       </c>
       <c r="AY53" t="n">
-        <v>84497.21090000001</v>
+        <v>84853.10159999999</v>
       </c>
       <c r="AZ53" t="n">
-        <v>78122.8992</v>
+        <v>77700.9984</v>
       </c>
       <c r="BA53" t="n">
-        <v>71371.2369</v>
+        <v>71323.0563</v>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="BD53" t="n">
-        <v>2705.7256</v>
+        <v>2683.8191</v>
       </c>
       <c r="BE53" t="n">
-        <v>2773.5249</v>
+        <v>2720.188</v>
       </c>
       <c r="BF53" t="n">
-        <v>2651.0835</v>
+        <v>2672.7065</v>
       </c>
       <c r="BG53" t="n">
-        <v>2668.1511</v>
+        <v>2705.5371</v>
       </c>
       <c r="BH53" t="n">
-        <v>2467.9566</v>
+        <v>2452.2734</v>
       </c>
       <c r="BI53" t="n">
-        <v>2113.9653</v>
+        <v>2112.3804</v>
       </c>
       <c r="BK53" t="inlineStr">
         <is>
@@ -20914,7 +20926,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -20943,7 +20955,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC54" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -20993,49 +21005,49 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>3 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="AV54" t="n">
-        <v>84503.1875</v>
+        <v>84855.64840000001</v>
       </c>
       <c r="AW54" t="n">
-        <v>85019.3281</v>
+        <v>87146.35159999999</v>
       </c>
       <c r="AX54" t="n">
-        <v>84429.64840000001</v>
+        <v>83852.69530000001</v>
       </c>
       <c r="AY54" t="n">
-        <v>84763.5781</v>
+        <v>84497.21090000001</v>
       </c>
       <c r="AZ54" t="n">
-        <v>78558.65889999999</v>
+        <v>78122.8992</v>
       </c>
       <c r="BA54" t="n">
-        <v>71425.4424</v>
+        <v>71371.2369</v>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>3 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="BD54" t="n">
-        <v>2668.4485</v>
+        <v>2705.7256</v>
       </c>
       <c r="BE54" t="n">
-        <v>2689.594</v>
+        <v>2773.5249</v>
       </c>
       <c r="BF54" t="n">
-        <v>2665.4348</v>
+        <v>2651.0835</v>
       </c>
       <c r="BG54" t="n">
-        <v>2687.2554</v>
+        <v>2668.1511</v>
       </c>
       <c r="BH54" t="n">
-        <v>2484.0887</v>
+        <v>2467.9566</v>
       </c>
       <c r="BI54" t="n">
-        <v>2115.8113</v>
+        <v>2113.9653</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
@@ -21187,7 +21199,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -21216,7 +21228,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC55" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -21266,49 +21278,49 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>4 okt</t>
+          <t>3 okt</t>
         </is>
       </c>
       <c r="AV55" t="n">
-        <v>84765.5156</v>
+        <v>84503.1875</v>
       </c>
       <c r="AW55" t="n">
-        <v>86766.14840000001</v>
+        <v>85019.3281</v>
       </c>
       <c r="AX55" t="n">
-        <v>84707.32030000001</v>
+        <v>84429.64840000001</v>
       </c>
       <c r="AY55" t="n">
-        <v>86480.30469999999</v>
+        <v>84763.5781</v>
       </c>
       <c r="AZ55" t="n">
-        <v>79027.77860000001</v>
+        <v>78558.65889999999</v>
       </c>
       <c r="BA55" t="n">
-        <v>71501.6161</v>
+        <v>71425.4424</v>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>4 okt</t>
+          <t>3 okt</t>
         </is>
       </c>
       <c r="BD55" t="n">
-        <v>2687.3511</v>
+        <v>2668.4485</v>
       </c>
       <c r="BE55" t="n">
-        <v>2738.2566</v>
+        <v>2689.594</v>
       </c>
       <c r="BF55" t="n">
-        <v>2686.1321</v>
+        <v>2665.4348</v>
       </c>
       <c r="BG55" t="n">
-        <v>2726.509</v>
+        <v>2687.2554</v>
       </c>
       <c r="BH55" t="n">
-        <v>2501.0007</v>
+        <v>2484.0887</v>
       </c>
       <c r="BI55" t="n">
-        <v>2118.4254</v>
+        <v>2115.8113</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
@@ -21460,7 +21472,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -21489,7 +21501,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC56" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -21535,53 +21547,53 @@
         <v>1490.0724</v>
       </c>
       <c r="AS56" t="n">
-        <v>1332.1047</v>
+        <v>1332.1048</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>4 okt</t>
         </is>
       </c>
       <c r="AV56" t="n">
-        <v>86480.00780000001</v>
+        <v>84765.5156</v>
       </c>
       <c r="AW56" t="n">
-        <v>86971.7812</v>
+        <v>86766.14840000001</v>
       </c>
       <c r="AX56" t="n">
-        <v>84971.86719999999</v>
+        <v>84707.32030000001</v>
       </c>
       <c r="AY56" t="n">
-        <v>85786.5938</v>
+        <v>86480.30469999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>79487.13740000001</v>
+        <v>79027.77860000001</v>
       </c>
       <c r="BA56" t="n">
-        <v>71580.98510000001</v>
+        <v>71501.6161</v>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>4 okt</t>
         </is>
       </c>
       <c r="BD56" t="n">
-        <v>2726.6538</v>
+        <v>2687.3511</v>
       </c>
       <c r="BE56" t="n">
-        <v>2736.7852</v>
+        <v>2738.2566</v>
       </c>
       <c r="BF56" t="n">
-        <v>2679.355</v>
+        <v>2686.1321</v>
       </c>
       <c r="BG56" t="n">
-        <v>2711.0315</v>
+        <v>2726.509</v>
       </c>
       <c r="BH56" t="n">
-        <v>2517.7425</v>
+        <v>2501.0007</v>
       </c>
       <c r="BI56" t="n">
-        <v>2121.2935</v>
+        <v>2118.4254</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
@@ -21733,7 +21745,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -21762,7 +21774,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC57" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -21812,49 +21824,49 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="AV57" t="n">
-        <v>85785.66409999999</v>
+        <v>86480.00780000001</v>
       </c>
       <c r="AW57" t="n">
-        <v>86664.53909999999</v>
+        <v>86971.7812</v>
       </c>
       <c r="AX57" t="n">
-        <v>85119.55469999999</v>
+        <v>84971.86719999999</v>
       </c>
       <c r="AY57" t="n">
-        <v>85557.5625</v>
+        <v>85786.5938</v>
       </c>
       <c r="AZ57" t="n">
-        <v>79908.1636</v>
+        <v>79487.13740000001</v>
       </c>
       <c r="BA57" t="n">
-        <v>71656.16</v>
+        <v>71580.98510000001</v>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="BD57" t="n">
-        <v>2711.0271</v>
+        <v>2726.6538</v>
       </c>
       <c r="BE57" t="n">
-        <v>2723.7361</v>
+        <v>2736.7852</v>
       </c>
       <c r="BF57" t="n">
-        <v>2683.8933</v>
+        <v>2679.355</v>
       </c>
       <c r="BG57" t="n">
-        <v>2697.5164</v>
+        <v>2711.0315</v>
       </c>
       <c r="BH57" t="n">
-        <v>2533.4488</v>
+        <v>2517.7425</v>
       </c>
       <c r="BI57" t="n">
-        <v>2124.0486</v>
+        <v>2121.2935</v>
       </c>
       <c r="BK57" t="inlineStr">
         <is>
@@ -22006,7 +22018,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -22035,7 +22047,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC58" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -22085,49 +22097,49 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="AV58" t="n">
-        <v>85554.7969</v>
+        <v>85785.66409999999</v>
       </c>
       <c r="AW58" t="n">
-        <v>85594.5469</v>
+        <v>86664.53909999999</v>
       </c>
       <c r="AX58" t="n">
-        <v>82771.78909999999</v>
+        <v>85119.55469999999</v>
       </c>
       <c r="AY58" t="n">
-        <v>83275.92969999999</v>
+        <v>85557.5625</v>
       </c>
       <c r="AZ58" t="n">
-        <v>80280.068</v>
+        <v>79908.1636</v>
       </c>
       <c r="BA58" t="n">
-        <v>71728.982</v>
+        <v>71656.16</v>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="BD58" t="n">
-        <v>2697.3748</v>
+        <v>2711.0271</v>
       </c>
       <c r="BE58" t="n">
-        <v>2699.259</v>
+        <v>2723.7361</v>
       </c>
       <c r="BF58" t="n">
-        <v>2540.5916</v>
+        <v>2683.8933</v>
       </c>
       <c r="BG58" t="n">
-        <v>2573.5273</v>
+        <v>2697.5164</v>
       </c>
       <c r="BH58" t="n">
-        <v>2546.5902</v>
+        <v>2533.4488</v>
       </c>
       <c r="BI58" t="n">
-        <v>2126.5328</v>
+        <v>2124.0486</v>
       </c>
       <c r="BK58" t="inlineStr">
         <is>
@@ -22279,7 +22291,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -22308,7 +22320,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC59" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -22358,49 +22370,49 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="AV59" t="n">
-        <v>83281.4688</v>
+        <v>85554.7969</v>
       </c>
       <c r="AW59" t="n">
-        <v>83474.96090000001</v>
+        <v>85594.5469</v>
       </c>
       <c r="AX59" t="n">
-        <v>80336.9062</v>
+        <v>82771.78909999999</v>
       </c>
       <c r="AY59" t="n">
-        <v>81676.33590000001</v>
+        <v>83275.92969999999</v>
       </c>
       <c r="AZ59" t="n">
-        <v>80528.2709</v>
+        <v>80280.068</v>
       </c>
       <c r="BA59" t="n">
-        <v>71798.1376</v>
+        <v>71728.982</v>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="BD59" t="n">
-        <v>2573.5547</v>
+        <v>2697.3748</v>
       </c>
       <c r="BE59" t="n">
-        <v>2585.303</v>
+        <v>2699.259</v>
       </c>
       <c r="BF59" t="n">
-        <v>2406.1519</v>
+        <v>2540.5916</v>
       </c>
       <c r="BG59" t="n">
-        <v>2471.9126</v>
+        <v>2573.5273</v>
       </c>
       <c r="BH59" t="n">
-        <v>2550.9992</v>
+        <v>2546.5902</v>
       </c>
       <c r="BI59" t="n">
-        <v>2128.6271</v>
+        <v>2126.5328</v>
       </c>
       <c r="BK59" t="inlineStr">
         <is>
@@ -22552,7 +22564,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -22581,7 +22593,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC60" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -22631,49 +22643,49 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="AV60" t="n">
+        <v>83281.4688</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>83474.96090000001</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>80336.9062</v>
+      </c>
+      <c r="AY60" t="n">
         <v>81676.33590000001</v>
       </c>
-      <c r="AW60" t="n">
-        <v>83418.2969</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>81557.7031</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>82546.32030000001</v>
-      </c>
       <c r="AZ60" t="n">
-        <v>80718.5422</v>
+        <v>80528.2709</v>
       </c>
       <c r="BA60" t="n">
-        <v>71856.29489999999</v>
+        <v>71798.1376</v>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="BD60" t="n">
+        <v>2573.5547</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>2585.303</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>2406.1519</v>
+      </c>
+      <c r="BG60" t="n">
         <v>2471.9126</v>
       </c>
-      <c r="BE60" t="n">
-        <v>2514.897</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>2469.229</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>2485.5386</v>
-      </c>
       <c r="BH60" t="n">
-        <v>2554.1823</v>
+        <v>2550.9992</v>
       </c>
       <c r="BI60" t="n">
-        <v>2130.2941</v>
+        <v>2128.6271</v>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
@@ -22825,7 +22837,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -22854,7 +22866,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC61" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -22904,49 +22916,49 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>10 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="AV61" t="n">
+        <v>81676.33590000001</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>83418.2969</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>81557.7031</v>
+      </c>
+      <c r="AY61" t="n">
         <v>82546.32030000001</v>
       </c>
-      <c r="AW61" t="n">
-        <v>83092.0312</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>82473.03909999999</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>82912.22659999999</v>
-      </c>
       <c r="AZ61" t="n">
-        <v>80810.083</v>
+        <v>80718.5422</v>
       </c>
       <c r="BA61" t="n">
-        <v>71918.2668</v>
+        <v>71856.29489999999</v>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>10 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="BD61" t="n">
+        <v>2471.9126</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>2514.897</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>2469.229</v>
+      </c>
+      <c r="BG61" t="n">
         <v>2485.5386</v>
       </c>
-      <c r="BE61" t="n">
-        <v>2516.6155</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>2483.7974</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>2504.0278</v>
-      </c>
       <c r="BH61" t="n">
-        <v>2553.9572</v>
+        <v>2554.1823</v>
       </c>
       <c r="BI61" t="n">
-        <v>2132.0357</v>
+        <v>2130.2941</v>
       </c>
       <c r="BK61" t="inlineStr">
         <is>
@@ -23098,7 +23110,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -23127,7 +23139,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC62" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -23177,49 +23189,49 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>11 okt</t>
+          <t>10 okt</t>
         </is>
       </c>
       <c r="AV62" t="n">
+        <v>82546.32030000001</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>83092.0312</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>82473.03909999999</v>
+      </c>
+      <c r="AY62" t="n">
         <v>82912.22659999999</v>
       </c>
-      <c r="AW62" t="n">
-        <v>84103.625</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>82722.1094</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>83679.4688</v>
-      </c>
       <c r="AZ62" t="n">
-        <v>80942.00410000001</v>
+        <v>80810.083</v>
       </c>
       <c r="BA62" t="n">
-        <v>71980.11470000001</v>
+        <v>71918.2668</v>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>11 okt</t>
+          <t>10 okt</t>
         </is>
       </c>
       <c r="BD62" t="n">
+        <v>2485.5386</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>2516.6155</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>2483.7974</v>
+      </c>
+      <c r="BG62" t="n">
         <v>2504.0278</v>
       </c>
-      <c r="BE62" t="n">
-        <v>2551.5315</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>2495.7202</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>2534.6992</v>
-      </c>
       <c r="BH62" t="n">
-        <v>2556.1662</v>
+        <v>2553.9572</v>
       </c>
       <c r="BI62" t="n">
-        <v>2133.8691</v>
+        <v>2132.0357</v>
       </c>
       <c r="BK62" t="inlineStr">
         <is>
@@ -23371,7 +23383,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -23400,7 +23412,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC63" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -23450,49 +23462,49 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>11 okt</t>
         </is>
       </c>
       <c r="AV63" t="n">
+        <v>82912.22659999999</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>84103.625</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>82722.1094</v>
+      </c>
+      <c r="AY63" t="n">
         <v>83679.4688</v>
       </c>
-      <c r="AW63" t="n">
-        <v>84249.2188</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>81681.63280000001</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>81762.5625</v>
-      </c>
       <c r="AZ63" t="n">
-        <v>81022.14999999999</v>
+        <v>80942.00410000001</v>
       </c>
       <c r="BA63" t="n">
-        <v>72044.9694</v>
+        <v>71980.11470000001</v>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>11 okt</t>
         </is>
       </c>
       <c r="BD63" t="n">
+        <v>2504.0278</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>2551.5315</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>2495.7202</v>
+      </c>
+      <c r="BG63" t="n">
         <v>2534.6992</v>
       </c>
-      <c r="BE63" t="n">
-        <v>2576.5774</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>2441.6763</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>2444.3574</v>
-      </c>
       <c r="BH63" t="n">
-        <v>2555.777</v>
+        <v>2556.1662</v>
       </c>
       <c r="BI63" t="n">
-        <v>2135.793</v>
+        <v>2133.8691</v>
       </c>
       <c r="BK63" t="inlineStr">
         <is>
@@ -23644,7 +23656,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -23673,7 +23685,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC64" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -23723,49 +23735,49 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="AV64" t="n">
+        <v>83679.4688</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>84249.2188</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>81681.63280000001</v>
+      </c>
+      <c r="AY64" t="n">
         <v>81762.5625</v>
       </c>
-      <c r="AW64" t="n">
-        <v>84061.0938</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>80962.5156</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>83095.125</v>
-      </c>
       <c r="AZ64" t="n">
-        <v>81104.7628</v>
+        <v>81022.14999999999</v>
       </c>
       <c r="BA64" t="n">
-        <v>72128.7531</v>
+        <v>72044.9694</v>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="BD64" t="n">
+        <v>2534.6992</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>2576.5774</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>2441.6763</v>
+      </c>
+      <c r="BG64" t="n">
         <v>2444.3574</v>
       </c>
-      <c r="BE64" t="n">
-        <v>2534.77</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>2407.6274</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>2496.6255</v>
-      </c>
       <c r="BH64" t="n">
-        <v>2556.0729</v>
+        <v>2555.777</v>
       </c>
       <c r="BI64" t="n">
-        <v>2138.3197</v>
+        <v>2135.793</v>
       </c>
       <c r="BK64" t="inlineStr">
         <is>
@@ -23917,7 +23929,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -23946,7 +23958,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="AC65" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -23996,49 +24008,49 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="AV65" t="n">
+        <v>81762.5625</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>84061.0938</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>80962.5156</v>
+      </c>
+      <c r="AY65" t="n">
         <v>83095.125</v>
       </c>
-      <c r="AW65" t="n">
-        <v>84049.0625</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>81345.88280000001</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>81562.49219999999</v>
-      </c>
       <c r="AZ65" t="n">
-        <v>81164.71309999999</v>
+        <v>81104.7628</v>
       </c>
       <c r="BA65" t="n">
-        <v>72204.96709999999</v>
+        <v>72128.7531</v>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="BD65" t="n">
+        <v>2444.3574</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>2534.77</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>2407.6274</v>
+      </c>
+      <c r="BG65" t="n">
         <v>2496.6255</v>
       </c>
-      <c r="BE65" t="n">
-        <v>2526.0706</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>2403.2107</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>2418.207</v>
-      </c>
       <c r="BH65" t="n">
-        <v>2555.5739</v>
+        <v>2556.0729</v>
       </c>
       <c r="BI65" t="n">
-        <v>2140.4473</v>
+        <v>2138.3197</v>
       </c>
       <c r="BK65" t="inlineStr">
         <is>
@@ -24165,61 +24177,61 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>199.48</v>
+        <v>196.6</v>
       </c>
       <c r="M66" t="n">
-        <v>200.85</v>
+        <v>199.36</v>
       </c>
       <c r="N66" t="n">
-        <v>198</v>
+        <v>195.26</v>
       </c>
       <c r="O66" t="n">
-        <v>200.5</v>
+        <v>197.44</v>
       </c>
       <c r="P66" t="n">
-        <v>184.6868</v>
+        <v>184.6256</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9292</v>
+        <v>163.9139</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>46.295</v>
+        <v>45.95</v>
       </c>
       <c r="W66" t="n">
-        <v>46.635</v>
+        <v>46.675</v>
       </c>
       <c r="X66" t="n">
-        <v>46.29</v>
+        <v>45.91</v>
       </c>
       <c r="Y66" t="n">
-        <v>46.295</v>
+        <v>46.42</v>
       </c>
       <c r="Z66" t="n">
-        <v>41.1218</v>
+        <v>41.1243</v>
       </c>
       <c r="AA66" t="n">
-        <v>36.8175</v>
+        <v>36.8181</v>
       </c>
       <c r="AB66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="AC66" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -24246,118 +24258,118 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="AN66" t="n">
-        <v>1451.8</v>
+        <v>1510</v>
       </c>
       <c r="AO66" t="n">
-        <v>1455</v>
+        <v>1564</v>
       </c>
       <c r="AP66" t="n">
-        <v>1422.6</v>
+        <v>1494</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1441</v>
+        <v>1534.8</v>
       </c>
       <c r="AR66" t="n">
-        <v>1517.28</v>
+        <v>1519.156</v>
       </c>
       <c r="AS66" t="n">
-        <v>1366.3805</v>
+        <v>1366.8495</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="AV66" t="n">
-        <v>81573.10159999999</v>
+        <v>83095.125</v>
       </c>
       <c r="AW66" t="n">
-        <v>81773.7656</v>
+        <v>84049.0625</v>
       </c>
       <c r="AX66" t="n">
-        <v>80474.07030000001</v>
+        <v>81345.88280000001</v>
       </c>
       <c r="AY66" t="n">
-        <v>81413.99219999999</v>
+        <v>81562.49219999999</v>
       </c>
       <c r="AZ66" t="n">
-        <v>81212.4445</v>
+        <v>81164.71309999999</v>
       </c>
       <c r="BA66" t="n">
-        <v>72282.2625</v>
+        <v>72204.96709999999</v>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="BD66" t="n">
-        <v>2418.4326</v>
+        <v>2496.6255</v>
       </c>
       <c r="BE66" t="n">
-        <v>2424.9353</v>
+        <v>2526.0706</v>
       </c>
       <c r="BF66" t="n">
-        <v>2342.5146</v>
+        <v>2403.2107</v>
       </c>
       <c r="BG66" t="n">
-        <v>2376.51</v>
+        <v>2418.207</v>
       </c>
       <c r="BH66" t="n">
-        <v>2552.9789</v>
+        <v>2555.5739</v>
       </c>
       <c r="BI66" t="n">
-        <v>2142.417</v>
+        <v>2140.4473</v>
       </c>
       <c r="BK66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="BL66" t="n">
-        <v>50.7</v>
+        <v>56.64</v>
       </c>
       <c r="BM66" t="n">
-        <v>51.4</v>
+        <v>58.01</v>
       </c>
       <c r="BN66" t="n">
-        <v>49.9</v>
+        <v>54.65</v>
       </c>
       <c r="BO66" t="n">
-        <v>50.53</v>
+        <v>55.05</v>
       </c>
       <c r="BP66" t="n">
-        <v>58.0658</v>
+        <v>58.1562</v>
       </c>
       <c r="BQ66" t="n">
-        <v>56.4442</v>
+        <v>56.4668</v>
       </c>
       <c r="BS66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="BT66" t="n">
-        <v>129.97</v>
+        <v>132.08</v>
       </c>
       <c r="BU66" t="n">
-        <v>130.18</v>
+        <v>132.42</v>
       </c>
       <c r="BV66" t="n">
-        <v>129.94</v>
+        <v>131.75</v>
       </c>
       <c r="BW66" t="n">
-        <v>130.18</v>
+        <v>131.78</v>
       </c>
       <c r="BX66" t="n">
-        <v>128.2818</v>
+        <v>128.3138</v>
       </c>
       <c r="BY66" t="n">
-        <v>120.3785</v>
+        <v>120.3865</v>
       </c>
       <c r="CA66" t="inlineStr">
         <is>
@@ -24380,7 +24392,7 @@
         <v>982.2577</v>
       </c>
       <c r="CG66" t="n">
-        <v>711.5055</v>
+        <v>711.5056</v>
       </c>
       <c r="CI66" t="inlineStr">
         <is>
@@ -24565,7 +24577,7 @@
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  200,50 EUR</t>
+          <t>SAP (SAP.DE)  ·  197,44 EUR</t>
         </is>
       </c>
     </row>
@@ -24577,21 +24589,21 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>Gestegen: 45,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,7% (winst). De bot verkoopt als de koers onder 184,37 zakt (-8,0%).</t>
+          <t>Gestegen: 43,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 181,20 zakt (-8,2%).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,29 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,42 EUR</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Gestegen: 25,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,7% (winst). De bot verkoopt als de koers onder 43,59 zakt (-5,8%).</t>
+          <t>Gestegen: 25,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,0% (winst). De bot verkoopt als de koers onder 43,70 zakt (-5,9%).</t>
         </is>
       </c>
     </row>
@@ -24610,7 +24622,7 @@
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
-          <t>ASML (ASML.AS)  ·  1.441,00 EUR</t>
+          <t>ASML (ASML.AS)  ·  1.534,80 EUR</t>
         </is>
       </c>
     </row>
@@ -24622,55 +24634,55 @@
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>Gedaald: -9,7% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gedaald: -3,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="B94" s="31" t="inlineStr">
         <is>
-          <t>Bitcoin (BTC-USD)  ·  81.413,99 USD</t>
+          <t>Bitcoin (BTC-USD)  ·  81.562,49 USD</t>
         </is>
       </c>
       <c r="D94" s="31" t="inlineStr">
         <is>
-          <t>Ethereum (ETH-USD)  ·  2.376,51 USD</t>
+          <t>Ethereum (ETH-USD)  ·  2.418,21 USD</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="B95" s="34" t="inlineStr">
         <is>
-          <t>Gestegen: 28,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+          <t>Gestegen: 28,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
       <c r="D95" s="34" t="inlineStr">
         <is>
-          <t>Gestegen: 26,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="B115" s="31" t="inlineStr">
         <is>
-          <t>Infineon (IFX.DE)  ·  50,53 EUR</t>
+          <t>Infineon (IFX.DE)  ·  55,05 EUR</t>
         </is>
       </c>
       <c r="D115" s="31" t="inlineStr">
         <is>
-          <t>iShares MSCI World (IWDA.AS)  ·  130,18 EUR</t>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,78 EUR</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="B116" s="34" t="inlineStr">
         <is>
-          <t>Gedaald: -21,9% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gedaald: -14,9% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
       <c r="D116" s="34" t="inlineStr">
         <is>
-          <t>Gestegen: 3,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
@@ -24711,7 +24723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H25"/>
+  <dimension ref="B1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -24734,21 +24746,21 @@
     <row r="3" ht="21.4" customHeight="1">
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>• 6 van de 11 grafieken staan in een stijgende trend, 0 in een dalende, 5 zonder duidelijke richting.</t>
+          <t>• 7 van de 11 grafieken staan in een stijgende trend, 0 in een dalende, 4 zonder duidelijke richting.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="21.4" customHeight="1">
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>• Sterkste van de laatste maand: AMD (+13,2%); zwakste: Ethereum (-11,6%).</t>
+          <t>• Sterkste van de laatste maand: AMD (+13,2%); zwakste: Ethereum (-9,9%).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21.4" customHeight="1">
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>• Afgelopen week: 3 van de 11 gestegen, gemiddeld -5,3%.</t>
+          <t>• Afgelopen week: 4 van de 11 gestegen, gemiddeld -3,8%.</t>
         </is>
       </c>
     </row>
@@ -24762,72 +24774,96 @@
     <row r="7" ht="21.4" customHeight="1">
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>• Op of vlak bij hun laagste punt van 3 maanden: Infineon.</t>
+          <t>• Terugval binnen een stijgende trend: AMD, ASML.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.4" customHeight="1">
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>• Terugval binnen een stijgende trend: AMD.</t>
+          <t>• Net onder het 50-daags gemiddelde gezakt (voor de trend-agent een verkoopsignaal): ASML, Infineon, Micron, Halfgeleider-ETF.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21.4" customHeight="1">
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>• Net onder het 50-daags gemiddelde gezakt (voor de trend-agent een verkoopsignaal): ASML, Infineon, Micron, Halfgeleider-ETF.</t>
+          <t>• Dit beschrijft wat er gebeurd is; het voorspelt niet wat de koersen morgen doen.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="21.4" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>• Dit beschrijft wat er gebeurd is; het voorspelt niet wat de koersen morgen doen.</t>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Aandeel</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Maand</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>3 maanden</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Opvallend</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Samenvatting</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Aandeel</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>Maand</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>3 maanden</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>Opvallend</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>Samenvatting</t>
+    <row r="12" ht="67.8" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +35,2% in 3 maanden, +7,4% in de laatste maand en +0,7% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="67.8" customHeight="1">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)</t>
+          <t>SAP (SAP.DE)</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -24836,29 +24872,29 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.0074</v>
+        <v>0.0523</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.0736</v>
+        <v>0.0554</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.3515</v>
+        <v>0.4345</v>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug</t>
+          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep · 4 dagen op rij gestegen</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +35,2% in 3 maanden, +7,4% in de laatste maand en +0,7% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 28 aug.</t>
+          <t>Stijgende trend: +43,4% in 3 maanden, +5,5% in de laatste maand en +5,2% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep; 4 dagen op rij gestegen.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="67.8" customHeight="1">
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)</t>
+          <t>Shell (SHELL.AS)</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -24867,29 +24903,29 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.0717</v>
+        <v>0.0871</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>0.4567</v>
+        <v>0.2588</v>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands top · 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep · 4 dagen op rij gestegen</t>
+          <t>nieuwe 3-maands top · 10 dagen op rij gestegen · 9 van de laatste 10 dagen groen</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +45,7% in 3 maanden, +7,2% in de laatste maand en +6,9% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 50-daags gemiddelde kruiste omhoog door het 200-daagse op 14 sep; 4 dagen op rij gestegen.</t>
+          <t>Stijgende trend: +25,9% in 3 maanden, +8,7% in de laatste maand en +7,3% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 10 dagen op rij gestegen; 9 van de laatste 10 dagen groen.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="67.8" customHeight="1">
+    <row r="15" ht="51.85" customHeight="1">
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)</t>
+          <t>AMD (AMD)</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -24898,29 +24934,29 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.0704</v>
+        <v>-0.1162</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.0842</v>
+        <v>0.1321</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.2554</v>
+        <v>0.0788</v>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands top · 10 dagen op rij gestegen · 9 van de laatste 10 dagen groen</t>
+          <t>terugval binnen een stijgende trend</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +25,5% in 3 maanden, +8,4% in de laatste maand en +7,0% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 10 dagen op rij gestegen; 9 van de laatste 10 dagen groen.</t>
+          <t>Stijgende trend: +7,9% in 3 maanden, +13,2% in de laatste maand en -11,6% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: terugval binnen een stijgende trend.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="51.85" customHeight="1">
+    <row r="16" ht="67.8" customHeight="1">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>AMD (AMD)</t>
+          <t>ASML (ASML.AS)</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -24929,91 +24965,91 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>-0.1162</v>
+        <v>-0.0468</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>0.1321</v>
+        <v>0.1131</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>0.0788</v>
+        <v>-0.0386</v>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>terugval binnen een stijgende trend</t>
+          <t>net onder het 50-daags gemiddelde gezakt · net boven het 50-daags gemiddelde gestegen · terugval binnen een stijgende trend</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +7,9% in 3 maanden, +13,2% in de laatste maand en -11,6% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: terugval binnen een stijgende trend.</t>
+          <t>Stijgende trend: -3,9% in 3 maanden, +11,3% in de laatste maand en -4,7% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: net onder het 50-daags gemiddelde gezakt; net boven het 50-daags gemiddelde gestegen; terugval binnen een stijgende trend.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="51.85" customHeight="1">
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>ASML (ASML.AS)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+          <t>Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0334</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>Stijgende trend: +28,3% in 3 maanden, -3,3% in de laatste maand en -1,2% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="67.8" customHeight="1">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>zijwaarts</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
-        <v>-0.1051</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>-0.0974</v>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>net onder het 50-daags gemiddelde gezakt · 4 dagen op rij gedaald · grote beweging op de laatste dag (-4,5%) · 8 van de laatste 10 dagen rood</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>Geen duidelijke richting: -9,7% in 3 maanden, +4,5% in de laatste maand en -10,5% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 4 dagen op rij gedaald; grote beweging op de laatste dag (-4,5%).</t>
+      <c r="D18" s="19" t="n">
+        <v>-0.0271</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>-0.0993</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug · beweegt de laatste 2 weken veel meer dan daarvoor</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>Geen duidelijke richting: +28,5% in 3 maanden, -9,9% in de laatste maand en -2,7% in de laatste week. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug; beweegt de laatste 2 weken veel meer dan daarvoor.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="51.85" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Bitcoin (BTC-USD)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>stijgend</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>-0.0181</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>0.2841</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>Stijgende trend: +28,4% in 3 maanden, -3,5% in de laatste maand en -1,8% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 8 sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="67.8" customHeight="1">
+    <row r="19" ht="51.85" customHeight="1">
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Ethereum (ETH-USD)</t>
+          <t>Infineon (IFX.DE)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -25022,91 +25058,91 @@
         </is>
       </c>
       <c r="D19" s="19" t="n">
-        <v>-0.0509</v>
+        <v>-0.0968</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>-0.1157</v>
+        <v>0.0133</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>0.2654</v>
+        <v>-0.1493</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug · beweegt de laatste 2 weken veel meer dan daarvoor</t>
+          <t>net onder het 50-daags gemiddelde gezakt · 6 dagen op rij gedaald</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: +26,5% in 3 maanden, -11,6% in de laatste maand en -5,1% in de laatste week. Opvallend: 50-daags gemiddelde kruiste omhoog door het 200-daagse op 31 aug; beweegt de laatste 2 weken veel meer dan daarvoor.</t>
+          <t>Geen duidelijke richting: -14,9% in 3 maanden, +1,3% in de laatste maand en -9,7% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 6 dagen op rij gedaald.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="51.85" customHeight="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Infineon (IFX.DE)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>zijwaarts</t>
+          <t>iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>stijgend</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>-0.171</v>
+        <v>0.0025</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>-0.0699</v>
+        <v>0.0475</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-0.2191</v>
+        <v>0.0437</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands bodem · net onder het 50-daags gemiddelde gezakt · 6 dagen op rij gedaald · grote beweging op de laatste dag (-9,8%) · beweegt de laatste 2 weken veel meer dan daarvoor</t>
+          <t>nieuwe 3-maands top</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: -21,9% in 3 maanden, -7,0% in de laatste maand en -17,1% in de laatste week. Opvallend: nieuwe 3-maands bodem; net onder het 50-daags gemiddelde gezakt; 6 dagen op rij gedaald.</t>
+          <t>Stijgende trend: +4,4% in 3 maanden, +4,7% in de laatste maand en +0,3% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="51.85" customHeight="1">
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>iShares MSCI World (IWDA.AS)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>stijgend</t>
+          <t>Micron (MU)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>zijwaarts</t>
         </is>
       </c>
       <c r="D21" s="19" t="n">
-        <v>-0.0097</v>
+        <v>-0.1597</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.0347</v>
+        <v>-0.0144</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.031</v>
+        <v>0.0111</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands top</t>
+          <t>net onder het 50-daags gemiddelde gezakt · 5 dagen op rij gedaald</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +3,1% in 3 maanden, +3,5% in de laatste maand en -1,0% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top.</t>
+          <t>Geen duidelijke richting: +1,1% in 3 maanden, -1,4% in de laatste maand en -16,0% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 5 dagen op rij gedaald.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="51.85" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Micron (MU)</t>
+          <t>Halfgeleider-ETF (SMH)</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -25115,71 +25151,39 @@
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>-0.1597</v>
+        <v>-0.0965</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>-0.0144</v>
+        <v>0.0417</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.0111</v>
+        <v>-0.0441</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>net onder het 50-daags gemiddelde gezakt · 5 dagen op rij gedaald</t>
+          <t>net onder het 50-daags gemiddelde gezakt · 7 dagen op rij gedaald · grote beweging op de laatste dag (-4,0%) · veel handel op de laatste dag (1,9x normaal)</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: +1,1% in 3 maanden, -1,4% in de laatste maand en -16,0% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 5 dagen op rij gedaald.</t>
+          <t>Geen duidelijke richting: -4,4% in 3 maanden, +4,2% in de laatste maand en -9,6% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 7 dagen op rij gedaald; grote beweging op de laatste dag (-4,0%).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="51.85" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Halfgeleider-ETF (SMH)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>zijwaarts</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>-0.0965</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>-0.0441</v>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>net onder het 50-daags gemiddelde gezakt · 7 dagen op rij gedaald · grote beweging op de laatste dag (-4,0%) · veel handel op de laatste dag (1,9x normaal)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>Geen duidelijke richting: -4,4% in 3 maanden, +4,2% in de laatste maand en -9,6% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; 7 dagen op rij gedaald; grote beweging op de laatste dag (-4,0%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="20" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Dit beschrijft wat er gebeurd is; het voorspelt niet wat de koersen morgen doen. De bots gebruiken het niet om te beslissen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
@@ -25194,7 +25198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25232,7 +25236,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>koers 130,18, 8,1% boven het 200-daags gemiddelde (120,38); de afgelopen maand +3,5%. Trend: stijgend.</t>
+          <t>koers 131,78, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25253,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>10% op jaarbasis, tegen normaal 10% het afgelopen jaar: normaal.</t>
+          <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
@@ -25266,7 +25270,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>34 van de 50 instrumenten staan boven hun 200-daags gemiddelde (68%; EU 12 van 23, US 22 van 27).</t>
+          <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25304,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>12,6% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>13,0% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -25317,7 +25321,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>10,9% boven het 200-daags gemiddelde (mag in de mix).</t>
+          <t>13,0% boven het 200-daags gemiddelde (mag in de mix).</t>
         </is>
       </c>
     </row>
@@ -25368,7 +25372,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>koers 130,18, 8,1% boven het 200-daags gemiddelde (120,38); de afgelopen maand +3,5%. Trend: stijgend.</t>
+          <t>koers 131,78, 9,5% boven het 200-daags gemiddelde (120,39); de afgelopen maand +4,8%. Trend: stijgend.</t>
         </is>
       </c>
     </row>
@@ -25385,7 +25389,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>10% op jaarbasis, tegen normaal 10% het afgelopen jaar: normaal.</t>
+          <t>8% op jaarbasis, tegen normaal 10% het afgelopen jaar: laag.</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25406,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>34 van de 50 instrumenten staan boven hun 200-daags gemiddelde (68%; EU 12 van 23, US 22 van 27).</t>
+          <t>35 van de 50 instrumenten staan boven hun 200-daags gemiddelde (70%; EU 13 van 23, US 22 van 27).</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25440,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 28; niet gestegen over 1 of 3 maanden: 26; te weinig handel: 1.</t>
+          <t>geen stijgende trend (koers niet boven 50- en 200-daags gemiddelde): 26; niet gestegen over 1 of 3 maanden: 27; te weinig handel: 1.</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25457,7 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>17. Koopbare trends: 17.</t>
+          <t>18. Koopbare trends: 18.</t>
         </is>
       </c>
     </row>
@@ -25487,11 +25491,11 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 52% in een stijgende trend).</t>
+          <t>De markt is rustig: stops liggen dichterbij, posities kunnen iets groter.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="35.9" customHeight="1">
+    <row r="18" ht="19.95" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
@@ -25504,22 +25508,39 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
+          <t>Amerika staat er duidelijk beter voor dan Europa (81% tegen 57% in een stijgende trend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35.9" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Trend-agent</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Conclusie</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
           <t>3 van de 5 sterkste staan al ver boven hun gemiddelde (SHELL.AS, WKL.AS, XOM): de trend is sterk, maar instappen op zo'n moment kost vaker een terugval.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20" ht="19.95" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Trend-agent</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Conclusie</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Alle plekken zijn bezet, dus de bot koopt niets bij, hoe sterk een trend ook is.</t>
         </is>
@@ -25619,26 +25640,26 @@
         <v>45.0575</v>
       </c>
       <c r="D2" t="n">
-        <v>46.295</v>
+        <v>46.42</v>
       </c>
       <c r="E2" t="n">
-        <v>43.5896</v>
+        <v>43.6975</v>
       </c>
       <c r="F2" s="22" t="n">
-        <v>16.09</v>
+        <v>17.71</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>0.0275</v>
+        <v>0.0302</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>0.0621</v>
+        <v>0.0623</v>
       </c>
       <c r="I2" s="22" t="n">
-        <v>-20.08</v>
+        <v>-18.68</v>
       </c>
       <c r="J2" s="17" t="inlineStr">
         <is>
-          <t>Staat €16,09 in de plus. Zakt de koers 6,2% naar 43,59, dan verkoopt de bot met ongeveer €20,08 verlies.</t>
+          <t>Staat €17,71 in de plus. Zakt de koers 6,2% naar 43,70, dan verkoopt de bot met ongeveer €18,68 verlies.</t>
         </is>
       </c>
     </row>
@@ -25657,26 +25678,26 @@
         <v>191.5557</v>
       </c>
       <c r="D3" t="n">
-        <v>200.5</v>
+        <v>197.44</v>
       </c>
       <c r="E3" t="n">
-        <v>184.3707</v>
+        <v>181.1971</v>
       </c>
       <c r="F3" s="22" t="n">
-        <v>17.89</v>
+        <v>11.77</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>0.0467</v>
+        <v>0.0307</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="I3" s="22" t="n">
-        <v>-15.37</v>
+        <v>-21.72</v>
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>Staat €17,89 in de plus. Zakt de koers 8,8% naar 184,37, dan verkoopt de bot met ongeveer €15,37 verlies.</t>
+          <t>Staat €11,77 in de plus. Zakt de koers 9,0% naar 181,20, dan verkoopt de bot met ongeveer €21,72 verlies.</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25764,7 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>-0.05</v>
@@ -25756,7 +25777,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>-0.01</v>
@@ -25812,160 +25833,160 @@
       <c r="A12" s="17" t="inlineStr"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
-        <v>513.97</v>
+        <v>551.6799999999999</v>
       </c>
       <c r="D12" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-86.03</v>
+        <v>-48.32</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.1434</v>
+        <v>-0.0805</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="17" t="inlineStr"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>IWDA.AS</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>5926.17</v>
+        <v>559.95</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-73.83</v>
+        <v>-40.05</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0123</v>
+        <v>-0.0668</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="17" t="inlineStr"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
-        <v>538.67</v>
+        <v>570.38</v>
       </c>
       <c r="D14" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-61.33</v>
+        <v>-29.62</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>-0.1022</v>
+        <v>-0.0494</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="17" t="inlineStr"/>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>551.62</v>
+        <v>573.37</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-48.38</v>
+        <v>-26.63</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.0806</v>
+        <v>-0.0444</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="17" t="inlineStr"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
-        <v>570.3200000000001</v>
+        <v>573.73</v>
       </c>
       <c r="D16" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-29.68</v>
+        <v>-26.27</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>-0.0495</v>
+        <v>-0.0438</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="17" t="inlineStr"/>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>573.3</v>
+        <v>484.62</v>
       </c>
       <c r="D17" s="26" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-26.7</v>
+        <v>-15.38</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.0445</v>
+        <v>-0.0308</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="17" t="inlineStr"/>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
-        <v>476.21</v>
+        <v>490.3</v>
       </c>
       <c r="D18" s="26" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-23.79</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>-0.0476</v>
+        <v>-0.0194</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="17" t="inlineStr"/>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>BTC-USD</t>
+          <t>IWDA.AS</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>489.35</v>
+        <v>5999.01</v>
       </c>
       <c r="D19" s="26" t="n">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>-10.65</v>
+        <v>-0.99</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.0213</v>
+        <v>-0.0002</v>
       </c>
     </row>
   </sheetData>
@@ -26017,7 +26038,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +6,7% van het 20-daags gemiddelde (3,4x de normale dagbeweging) en RSI is 80; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Opgelopen: de koers staat +6,9% van het 20-daags gemiddelde (3,6x de normale dagbeweging) en RSI is 81; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -26029,7 +26050,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Shell steeg +22,9% in 3 maanden en +8,4% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
+          <t>Shell steeg +23,3% in 3 maanden en +8,7% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,0x het normale volume; beweegt gemiddeld 1,9% per dag</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26062,7 @@
       </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>Koop 13 stuks rond 46,32 EUR (inzet €602,14). Stop-loss op 44,51 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,45.</t>
+          <t>Koop 13 stuks rond 46,44 EUR (inzet €603,76). Stop-loss op 44,63 EUR (-3,9%). Gaat het mis, dan is het verlies ongeveer €25,59.</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26093,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +6,3% van het 20-daags gemiddelde, RSI 70</t>
+          <t>Neutraal: de koers staat +4,8% van het 20-daags gemiddelde, RSI 67</t>
         </is>
       </c>
     </row>
@@ -26084,7 +26105,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>SAP steeg +45,4% in 3 maanden en +7,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
+          <t>SAP steeg +43,2% in 3 maanden en +5,5% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 0,8x het normale volume; beweegt gemiddeld 2,7% per dag</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26117,7 @@
       </c>
       <c r="C13" s="29" t="inlineStr">
         <is>
-          <t>Koop 2 stuks rond 200,60 EUR (inzet €401,20). Stop-loss op 189,85 EUR (-5,4%). Gaat het mis, dan is het verlies ongeveer €23,51.</t>
+          <t>Koop 2 stuks rond 197,54 EUR (inzet €395,08). Stop-loss op 186,71 EUR (-5,5%). Gaat het mis, dan is het verlies ongeveer €23,66.</t>
         </is>
       </c>
     </row>
@@ -26115,19 +26136,19 @@
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>3. Wolters Kluwer (WKL.AS)</t>
+          <t>3. Energie-ETF (XLE)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38.8" customHeight="1">
-      <c r="B17" s="27" t="inlineStr">
+    <row r="17" ht="21.4" customHeight="1">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Opgelopen: de koers staat +11,3% van het 20-daags gemiddelde (4,1x de normale dagbeweging) en RSI is 78; na zo'n sprint volgt vaak eerst een terugval</t>
+          <t>Neutraal: de koers staat +5,2% van het 20-daags gemiddelde, RSI 72</t>
         </is>
       </c>
     </row>
@@ -26139,7 +26160,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Wolters Kluwer steeg +31,3% in 3 maanden en +16,5% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,7% per dag</t>
+          <t>Energie-ETF steeg +19,3% in 3 maanden en +3,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
         </is>
       </c>
     </row>
@@ -26151,7 +26172,7 @@
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
-          <t>Koop 5 stuks rond 80,02 EUR (inzet €400,10). Stop-loss op 75,63 EUR (-5,5%). Gaat het mis, dan is het verlies ongeveer €23,94.</t>
+          <t>Koop 11 stuks rond 67,66 USD (inzet €663,77). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,98.</t>
         </is>
       </c>
     </row>
@@ -26170,19 +26191,19 @@
     <row r="22">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>4. Energie-ETF (XLE)</t>
+          <t>4. Wolters Kluwer (WKL.AS)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="21.4" customHeight="1">
-      <c r="B23" s="28" t="inlineStr">
+    <row r="23" ht="38.8" customHeight="1">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Instapmoment</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Neutraal: de koers staat +5,2% van het 20-daags gemiddelde, RSI 72</t>
+          <t>Opgelopen: de koers staat +9,0% van het 20-daags gemiddelde (3,2x de normale dagbeweging) en RSI is 73; na zo'n sprint volgt vaak eerst een terugval</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26215,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Energie-ETF steeg +19,3% in 3 maanden en +3,2% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,1x het normale volume; beweegt gemiddeld 1,8% per dag</t>
+          <t>Wolters Kluwer steeg +28,3% in 3 maanden en +13,8% in 1 maand; koers boven het 50-daags en dat boven het 200-daags gemiddelde; MACD positief (de stijging versnelt); handel 1,2x het normale volume; beweegt gemiddeld 2,8% per dag</t>
         </is>
       </c>
     </row>
@@ -26206,7 +26227,7 @@
       </c>
       <c r="C25" s="29" t="inlineStr">
         <is>
-          <t>Koop 11 stuks rond 67,66 USD (inzet €663,77). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,98.</t>
+          <t>Koop 5 stuks rond 78,18 EUR (inzet €390,90). Stop-loss op 73,76 EUR (-5,7%). Gaat het mis, dan is het verlies ongeveer €24,10.</t>
         </is>
       </c>
     </row>
@@ -26360,7 +26381,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe -1,89%</t>
+          <t>verschil tot nu toe -1,47%</t>
         </is>
       </c>
     </row>
@@ -26382,7 +26403,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>bot -3,60%, ETF -1,57%</t>
+          <t>bot -1,97%, ETF -0,36%</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26466,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe +1,72%</t>
+          <t>verschil tot nu toe +0,47%</t>
         </is>
       </c>
     </row>
@@ -26638,19 +26659,19 @@
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>9639.620000000001</v>
+        <v>9803.040000000001</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>-360.38</v>
+        <v>-196.96</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>10029.19</v>
+        <v>10024.69</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>29.19</v>
+        <v>24.69</v>
       </c>
       <c r="F5" t="n">
-        <v>130.18</v>
+        <v>131.78</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/dagrapport.xlsx
+++ b/rapporten/dagrapport.xlsx
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9803.040000000001</v>
+        <v>9799.15</v>
       </c>
     </row>
     <row r="6">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-196.96</v>
+        <v>-200.85</v>
       </c>
     </row>
     <row r="7">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.01969599999999994</v>
+        <v>-0.02008500000000002</v>
       </c>
     </row>
     <row r="8">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>-182.5799999999999</v>
+        <v>-186.4700000000012</v>
       </c>
     </row>
     <row r="9">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>-0.01465507763084839</v>
+        <v>-0.01504463781839815</v>
       </c>
     </row>
     <row r="11">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10024.69</v>
+        <v>10024.11</v>
       </c>
     </row>
     <row r="15">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>24.69</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="16">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.002469000000000054</v>
+        <v>0.002411000000000163</v>
       </c>
     </row>
     <row r="17">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>10.27000000000044</v>
+        <v>9.690000000000509</v>
       </c>
     </row>
     <row r="18">
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.004654736380648616</v>
+        <v>0.004596819896219184</v>
       </c>
     </row>
     <row r="20">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 52 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (ophalen mislukt: URLError).</t>
+          <t>Koersbronnen: 0 bevestigd door twee bronnen, 50 uit één bron, 0 afwijkend. Wisselkoers: bevestigd. Tweede bron overgeslagen na herhaalde fouten (GOOGL: Stooq gaf geen koersen ('&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta charset')).</t>
         </is>
       </c>
     </row>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="KO4" t="n">
-        <v>9803.040000000001</v>
+        <v>9799.15</v>
       </c>
       <c r="KP4" t="n">
-        <v>10024.69</v>
+        <v>10024.11</v>
       </c>
       <c r="KQ4" t="n">
         <v>9949.379999999999</v>
@@ -7736,7 +7736,7 @@
         <v>865.3239</v>
       </c>
       <c r="CF5" t="n">
-        <v>937.4059999999999</v>
+        <v>937.4059</v>
       </c>
       <c r="CG5" t="n">
         <v>486.3243</v>
@@ -8282,7 +8282,7 @@
         <v>959.329</v>
       </c>
       <c r="CF7" t="n">
-        <v>948.1458</v>
+        <v>948.1457</v>
       </c>
       <c r="CG7" t="n">
         <v>494.148</v>
@@ -8828,7 +8828,7 @@
         <v>920.8051</v>
       </c>
       <c r="CF9" t="n">
-        <v>955.1345</v>
+        <v>955.1344</v>
       </c>
       <c r="CG9" t="n">
         <v>501.8105</v>
@@ -9647,7 +9647,7 @@
         <v>738.8837</v>
       </c>
       <c r="CF12" t="n">
-        <v>958.2497</v>
+        <v>958.2496</v>
       </c>
       <c r="CG12" t="n">
         <v>511.2377</v>
@@ -9808,7 +9808,7 @@
         <v>1535.6006</v>
       </c>
       <c r="AS13" t="n">
-        <v>1204.2381</v>
+        <v>1204.238</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>1541.0191</v>
       </c>
       <c r="AS17" t="n">
-        <v>1215.9399</v>
+        <v>1215.9398</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>877.4319</v>
       </c>
       <c r="CF19" t="n">
-        <v>970.7131000000001</v>
+        <v>970.713</v>
       </c>
       <c r="CG19" t="n">
         <v>534.7758</v>
@@ -13742,7 +13742,7 @@
         <v>936.9625</v>
       </c>
       <c r="CF27" t="n">
-        <v>962.1174999999999</v>
+        <v>962.1174</v>
       </c>
       <c r="CG27" t="n">
         <v>563.4435999999999</v>
@@ -24392,7 +24392,7 @@
         <v>982.2577</v>
       </c>
       <c r="CG66" t="n">
-        <v>711.5056</v>
+        <v>711.5055</v>
       </c>
       <c r="CI66" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>509.899</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>-1.79</v>
+        <v>-2.38</v>
       </c>
       <c r="G4" s="23" t="n">
         <v>-0.0031</v>
@@ -25731,11 +25731,11 @@
         <v>0.0467</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>-24.01</v>
+        <v>-24.57</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>Staat €1,79 in de min. Zakt de koers 4,7% naar 509,90, dan verkoopt de bot met ongeveer €24,01 verlies.</t>
+          <t>Staat €2,38 in de min. Zakt de koers 4,7% naar 509,90, dan verkoopt de bot met ongeveer €24,57 verlies.</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>-0.05</v>
@@ -25837,16 +25837,16 @@
         </is>
       </c>
       <c r="C12" s="26" t="n">
-        <v>551.6799999999999</v>
+        <v>550.88</v>
       </c>
       <c r="D12" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-48.32</v>
+        <v>-49.12</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.0805</v>
+        <v>-0.0819</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -25877,16 +25877,16 @@
         </is>
       </c>
       <c r="C14" s="26" t="n">
-        <v>570.38</v>
+        <v>569.55</v>
       </c>
       <c r="D14" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-29.62</v>
+        <v>-30.45</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>-0.0494</v>
+        <v>-0.0507</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -25897,16 +25897,16 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>573.37</v>
+        <v>572.53</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>600</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-26.63</v>
+        <v>-27.47</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.0444</v>
+        <v>-0.0458</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -25937,16 +25937,16 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>484.62</v>
+        <v>483.91</v>
       </c>
       <c r="D17" s="26" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-15.38</v>
+        <v>-16.09</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.0308</v>
+        <v>-0.0322</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -25957,16 +25957,16 @@
         </is>
       </c>
       <c r="C18" s="26" t="n">
-        <v>490.3</v>
+        <v>489.58</v>
       </c>
       <c r="D18" s="26" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>-0.0194</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
-          <t>Koop 11 stuks rond 67,66 USD (inzet €663,77). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,98.</t>
+          <t>Koop 11 stuks rond 67,66 USD (inzet €662,95). Stop-loss op 65,22 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €25,95.</t>
         </is>
       </c>
     </row>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="C31" s="29" t="inlineStr">
         <is>
-          <t>Koop 4 stuks rond 177,10 USD (inzet €631,75). Stop-loss op 170,67 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €24,92.</t>
+          <t>Koop 4 stuks rond 177,10 USD (inzet €630,97). Stop-loss op 170,67 USD (-3,6%). Gaat het mis, dan is het verlies ongeveer €24,89.</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe -1,47%</t>
+          <t>verschil tot nu toe -1,50%</t>
         </is>
       </c>
     </row>
@@ -26403,7 +26403,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>bot -1,97%, ETF -0,36%</t>
+          <t>bot -2,01%, ETF -0,36%</t>
         </is>
       </c>
     </row>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe +0,47%</t>
+          <t>verschil tot nu toe +0,46%</t>
         </is>
       </c>
     </row>
@@ -26659,16 +26659,16 @@
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>9803.040000000001</v>
+        <v>9799.15</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>-196.96</v>
+        <v>-200.85</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>10024.69</v>
+        <v>10024.11</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>24.69</v>
+        <v>24.11</v>
       </c>
       <c r="F5" t="n">
         <v>131.78</v>

--- a/rapporten/dagrapport.xlsx
+++ b/rapporten/dagrapport.xlsx
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9438.940000000001</v>
+        <v>9438.120000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-561.0599999999999</v>
+        <v>-561.88</v>
       </c>
     </row>
     <row r="7">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.05610599999999999</v>
+        <v>-0.0561879999999999</v>
       </c>
     </row>
     <row r="8">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>-329.5199999999986</v>
+        <v>-330.3399999999983</v>
       </c>
     </row>
     <row r="9">
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>-0.03539091148653195</v>
+        <v>-0.03547302957233933</v>
       </c>
     </row>
     <row r="11">
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10083.15</v>
+        <v>10078.53</v>
       </c>
     </row>
     <row r="15">
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>83.15000000000001</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="16">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.008315000000000072</v>
+        <v>0.00785300000000011</v>
       </c>
     </row>
     <row r="17">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>15.35999999999876</v>
+        <v>10.73999999999978</v>
       </c>
     </row>
     <row r="18">
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.02621891771004659</v>
+        <v>0.02575758295476394</v>
       </c>
     </row>
     <row r="20">
@@ -9980,7 +9980,7 @@
         <v>1470.6326</v>
       </c>
       <c r="CP3" t="n">
-        <v>1535.0509</v>
+        <v>1535.051</v>
       </c>
       <c r="CQ3" t="n">
         <v>1208.2668</v>
@@ -11787,7 +11787,7 @@
         <v>877.4319</v>
       </c>
       <c r="ED7" t="n">
-        <v>970.7131000000001</v>
+        <v>970.713</v>
       </c>
       <c r="EE7" t="n">
         <v>534.7758</v>
@@ -12542,7 +12542,7 @@
         <v>1564.9065</v>
       </c>
       <c r="CP9" t="n">
-        <v>1547.2469</v>
+        <v>1547.247</v>
       </c>
       <c r="CQ9" t="n">
         <v>1227.0882</v>
@@ -15267,7 +15267,7 @@
         <v>936.9625</v>
       </c>
       <c r="ED15" t="n">
-        <v>962.1174999999999</v>
+        <v>962.1174</v>
       </c>
       <c r="EE15" t="n">
         <v>563.4435999999999</v>
@@ -15736,10 +15736,10 @@
         </is>
       </c>
       <c r="KO16" t="n">
-        <v>9438.940000000001</v>
+        <v>9438.120000000001</v>
       </c>
       <c r="KP16" t="n">
-        <v>10083.15</v>
+        <v>10078.53</v>
       </c>
       <c r="KQ16" t="n">
         <v>9792.34</v>
@@ -31606,7 +31606,7 @@
         <v>982.2577</v>
       </c>
       <c r="EE54" t="n">
-        <v>711.5056</v>
+        <v>711.5055</v>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
@@ -36269,10 +36269,10 @@
         <v>234.01</v>
       </c>
       <c r="M66" t="n">
-        <v>236.46</v>
+        <v>236.48</v>
       </c>
       <c r="N66" t="n">
-        <v>233.2224</v>
+        <v>233.22</v>
       </c>
       <c r="O66" t="n">
         <v>235.52</v>
@@ -36443,19 +36443,19 @@
         <v>69.52</v>
       </c>
       <c r="BU66" t="n">
-        <v>70.151</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="BV66" t="n">
-        <v>69.29000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="BW66" t="n">
-        <v>70</v>
+        <v>70.02</v>
       </c>
       <c r="BX66" t="n">
-        <v>64.7769</v>
+        <v>64.7773</v>
       </c>
       <c r="BY66" t="n">
-        <v>58.1515</v>
+        <v>58.1516</v>
       </c>
       <c r="BZ66" t="n">
         <v>70.035</v>
@@ -36469,22 +36469,22 @@
         </is>
       </c>
       <c r="CD66" t="n">
-        <v>510.12</v>
+        <v>508.53</v>
       </c>
       <c r="CE66" t="n">
-        <v>520.3955999999999</v>
+        <v>520.4</v>
       </c>
       <c r="CF66" t="n">
-        <v>492.24</v>
+        <v>492.21</v>
       </c>
       <c r="CG66" t="n">
-        <v>505.18</v>
+        <v>504.8</v>
       </c>
       <c r="CH66" t="n">
-        <v>548.2978000000001</v>
+        <v>548.2902</v>
       </c>
       <c r="CI66" t="n">
-        <v>410.4906</v>
+        <v>410.4887</v>
       </c>
       <c r="CK66" t="inlineStr">
         <is>
@@ -36607,22 +36607,22 @@
         </is>
       </c>
       <c r="DZ66" t="n">
-        <v>883.04</v>
+        <v>884</v>
       </c>
       <c r="EA66" t="n">
         <v>906.54</v>
       </c>
       <c r="EB66" t="n">
-        <v>861.585</v>
+        <v>861.59</v>
       </c>
       <c r="EC66" t="n">
-        <v>884.89</v>
+        <v>884.74</v>
       </c>
       <c r="ED66" t="n">
-        <v>978.5952</v>
+        <v>978.5922</v>
       </c>
       <c r="EE66" t="n">
-        <v>746.6257000000001</v>
+        <v>746.6249</v>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
@@ -36639,13 +36639,13 @@
         <v>511.63</v>
       </c>
       <c r="EK66" t="n">
-        <v>522.83</v>
+        <v>522.49</v>
       </c>
       <c r="EL66" t="n">
-        <v>572.6224</v>
+        <v>572.6156</v>
       </c>
       <c r="EM66" t="n">
-        <v>519.5027</v>
+        <v>519.501</v>
       </c>
     </row>
   </sheetData>
@@ -36879,7 +36879,7 @@
       </c>
       <c r="D92" s="32" t="inlineStr">
         <is>
-          <t>Energie-ETF (XLE)  ·  70,00 USD</t>
+          <t>Energie-ETF (XLE)  ·  70,02 USD</t>
         </is>
       </c>
     </row>
@@ -36891,7 +36891,7 @@
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>Gestegen: 18,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: nog vrijwel gelijk. De bot verkoopt als de koers onder 67,18 zakt (-4,0%).</t>
+          <t>Gestegen: 18,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: nog vrijwel gelijk. De bot verkoopt als de koers onder 67,18 zakt (-4,1%).</t>
         </is>
       </c>
     </row>
@@ -36905,7 +36905,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="B115" s="32" t="inlineStr">
         <is>
-          <t>AMD (AMD)  ·  505,18 USD</t>
+          <t>AMD (AMD)  ·  504,80 USD</t>
         </is>
       </c>
       <c r="D115" s="32" t="inlineStr">
@@ -36917,7 +36917,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="B116" s="35" t="inlineStr">
         <is>
-          <t>Gestegen: 6,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gestegen: 6,0% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
       <c r="D116" s="35" t="inlineStr">
@@ -36977,12 +36977,12 @@
     <row r="178" ht="22" customHeight="1">
       <c r="B178" s="32" t="inlineStr">
         <is>
-          <t>Micron (MU)  ·  884,89 USD</t>
+          <t>Micron (MU)  ·  884,74 USD</t>
         </is>
       </c>
       <c r="D178" s="32" t="inlineStr">
         <is>
-          <t>Halfgeleider-ETF (SMH)  ·  522,83 USD</t>
+          <t>Halfgeleider-ETF (SMH)  ·  522,49 USD</t>
         </is>
       </c>
     </row>
@@ -37346,13 +37346,13 @@
         </is>
       </c>
       <c r="D19" s="19" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.1164</v>
+        <v>0.1167</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>0.1825</v>
+        <v>0.1828</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Stijgende trend: +18,2% in 3 maanden, +11,6% in de laatste maand en +1,0% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 3 dagen op rij gestegen.</t>
+          <t>Stijgende trend: +18,3% in 3 maanden, +11,7% in de laatste maand en +1,0% in de laatste week. Het 50-daags gemiddelde loopt nog op. Opvallend: nieuwe 3-maands top; 3 dagen op rij gestegen.</t>
         </is>
       </c>
     </row>
@@ -37377,22 +37377,22 @@
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>-0.0225</v>
+        <v>-0.0232</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>-0.1795</v>
+        <v>-0.1802</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>0.061</v>
+        <v>0.0602</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>net onder het 50-daags gemiddelde gezakt · grote beweging op de laatste dag (-10,8%) · veel handel op de laatste dag (7,2x normaal)</t>
+          <t>net onder het 50-daags gemiddelde gezakt · grote beweging op de laatste dag (-10,9%) · veel handel op de laatste dag (2,0x normaal)</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: +6,1% in 3 maanden, -18,0% in de laatste maand en -2,2% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; grote beweging op de laatste dag (-10,8%); veel handel op de laatste dag (7,2x normaal).</t>
+          <t>Geen duidelijke richting: +6,0% in 3 maanden, -18,0% in de laatste maand en -2,3% in de laatste week. Opvallend: net onder het 50-daags gemiddelde gezakt; grote beweging op de laatste dag (-10,9%); veel handel op de laatste dag (2,0x normaal).</t>
         </is>
       </c>
     </row>
@@ -37551,7 +37551,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="67.8" customHeight="1">
+    <row r="26" ht="51.85" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Micron (MU)</t>
@@ -37563,22 +37563,22 @@
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>-0.1935</v>
+        <v>-0.1937</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>net boven het 50-daags gemiddelde gestegen · net onder het 50-daags gemiddelde gezakt · veel handel op de laatste dag (2,1x normaal)</t>
+          <t>net boven het 50-daags gemiddelde gestegen · net onder het 50-daags gemiddelde gezakt</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: +7,5% in 3 maanden, -19,4% in de laatste maand en +0,8% in de laatste week. Opvallend: net boven het 50-daags gemiddelde gestegen; net onder het 50-daags gemiddelde gezakt; veel handel op de laatste dag (2,1x normaal).</t>
+          <t>Geen duidelijke richting: +7,5% in 3 maanden, -19,4% in de laatste maand en +0,8% in de laatste week. Opvallend: net boven het 50-daags gemiddelde gestegen; net onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
     </row>
@@ -37594,22 +37594,22 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>-0.0083</v>
+        <v>-0.0089</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>-0.1537</v>
+        <v>-0.1543</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>-0.0327</v>
+        <v>-0.0334</v>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>nieuwe 3-maands bodem · grote beweging op de laatste dag (-6,9%) · beweegt de laatste 2 weken veel meer dan daarvoor · veel handel op de laatste dag (2,3x normaal)</t>
+          <t>nieuwe 3-maands bodem · grote beweging op de laatste dag (-7,0%) · beweegt de laatste 2 weken veel meer dan daarvoor · veel handel op de laatste dag (2,0x normaal)</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>Geen duidelijke richting: -3,3% in 3 maanden, -15,4% in de laatste maand en -0,8% in de laatste week. Opvallend: nieuwe 3-maands bodem; grote beweging op de laatste dag (-6,9%); beweegt de laatste 2 weken veel meer dan daarvoor.</t>
+          <t>Geen duidelijke richting: -3,3% in 3 maanden, -15,4% in de laatste maand en -0,9% in de laatste week. Opvallend: nieuwe 3-maands bodem; grote beweging op de laatste dag (-7,0%); beweegt de laatste 2 weken veel meer dan daarvoor.</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
         <v>511.5021</v>
       </c>
       <c r="F4" s="23" t="n">
-        <v>-10.31</v>
+        <v>-11.03</v>
       </c>
       <c r="G4" s="24" t="n">
         <v>-0.0251</v>
@@ -38123,11 +38123,11 @@
         <v>0.0203</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>-20.63</v>
+        <v>-21.33</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>Staat €10,31 in de min. Zakt de koers 2,0% naar 511,50, dan verkoopt de bot met ongeveer €20,63 verlies.</t>
+          <t>Staat €11,03 in de min. Zakt de koers 2,0% naar 511,50, dan verkoopt de bot met ongeveer €21,33 verlies.</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
         <v>277.381</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>8.6</v>
+        <v>7.79</v>
       </c>
       <c r="G6" s="24" t="n">
         <v>0.0136</v>
@@ -38199,11 +38199,11 @@
         <v>0.0631</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>-23.77</v>
+        <v>-24.53</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>Staat €8,60 in de plus. Zakt de koers 6,3% naar 277,38, dan verkoopt de bot met ongeveer €23,77 verlies.</t>
+          <t>Staat €7,79 in de plus. Zakt de koers 6,3% naar 277,38, dan verkoopt de bot met ongeveer €24,53 verlies.</t>
         </is>
       </c>
     </row>
@@ -38228,7 +38228,7 @@
         <v>226.1706</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>-0.53</v>
+        <v>-2.14</v>
       </c>
       <c r="G7" s="24" t="n">
         <v>-0.0005</v>
@@ -38237,11 +38237,11 @@
         <v>0.0413</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>-43.39</v>
+        <v>-44.94</v>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>Staat €0,53 in de min. Zakt de koers 4,1% naar 226,17, dan verkoopt de bot met ongeveer €43,39 verlies.</t>
+          <t>Staat €2,14 in de min. Zakt de koers 4,1% naar 226,17, dan verkoopt de bot met ongeveer €44,94 verlies.</t>
         </is>
       </c>
     </row>
@@ -38260,26 +38260,26 @@
         <v>70.035</v>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>70.02</v>
       </c>
       <c r="E8" t="n">
         <v>67.18340000000001</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>-0.6</v>
+        <v>-2.08</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>0.0419</v>
+        <v>0.0422</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>-49.52</v>
+        <v>-51.27</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>Staat €0,60 in de min. Zakt de koers 4,2% naar 67,18, dan verkoopt de bot met ongeveer €49,52 verlies.</t>
+          <t>Staat €2,08 in de min. Zakt de koers 4,2% naar 67,18, dan verkoopt de bot met ongeveer €51,27 verlies.</t>
         </is>
       </c>
     </row>
@@ -38346,7 +38346,7 @@
         </is>
       </c>
       <c r="B12" s="25" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>-0.1</v>
@@ -38359,7 +38359,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>0.0015</v>
+        <v>0.0011</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>-0.01</v>
@@ -38439,16 +38439,16 @@
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>508.76</v>
+        <v>508.38</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>600</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>-91.23999999999999</v>
+        <v>-91.62</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.1521</v>
+        <v>-0.1527</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -38499,16 +38499,16 @@
         </is>
       </c>
       <c r="C21" s="27" t="n">
-        <v>529.4299999999999</v>
+        <v>529.09</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>600</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>-70.56999999999999</v>
+        <v>-70.91</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>-0.1176</v>
+        <v>-0.1182</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -38519,16 +38519,16 @@
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>535.4299999999999</v>
+        <v>535.34</v>
       </c>
       <c r="D22" s="27" t="n">
         <v>600</v>
       </c>
       <c r="E22" s="23" t="n">
-        <v>-64.56999999999999</v>
+        <v>-64.66</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>-0.1076</v>
+        <v>-0.1078</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -38754,7 +38754,7 @@
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
-          <t>Koop 4 stuks rond 295,04 USD (inzet €1.056,94). Stop-loss op 281,10 USD (-4,7%). Gaat het mis, dan is het verlies ongeveer €51,94.</t>
+          <t>Koop 4 stuks rond 295,04 USD (inzet €1.055,33). Stop-loss op 281,10 USD (-4,7%). Gaat het mis, dan is het verlies ongeveer €51,86.</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
       </c>
       <c r="C25" s="29" t="inlineStr">
         <is>
-          <t>Koop 5 stuks rond 235,64 USD (inzet €1.055,19). Stop-loss op 226,17 USD (-4,0%). Gaat het mis, dan is het verlies ongeveer €44,39.</t>
+          <t>Koop 5 stuks rond 235,64 USD (inzet €1.053,57). Stop-loss op 226,17 USD (-4,0%). Gaat het mis, dan is het verlies ongeveer €44,34.</t>
         </is>
       </c>
     </row>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe -3,54%</t>
+          <t>verschil tot nu toe -3,55%</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38985,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>bot -5,61%, ETF -1,94%</t>
+          <t>bot -5,62%, ETF -1,94%</t>
         </is>
       </c>
     </row>
@@ -39048,7 +39048,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>verschil tot nu toe +2,62%</t>
+          <t>verschil tot nu toe +2,58%</t>
         </is>
       </c>
     </row>
@@ -39505,16 +39505,16 @@
         </is>
       </c>
       <c r="B17" s="27" t="n">
-        <v>9438.940000000001</v>
+        <v>9438.120000000001</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>-561.0599999999999</v>
+        <v>-561.88</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>10083.15</v>
+        <v>10078.53</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>83.15000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="F17" t="n">
         <v>129.7</v>
